--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -50,7 +50,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-百分比</t>
+百分比
+只针对有奖励的服务能力</t>
         </r>
       </text>
     </comment>
@@ -72,7 +73,10 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-概率_道具ID_数量</t>
+不同的星级影响特殊材料掉落的概率；
+万分比；
+这边空值时，直接读取等级表的概率；
+这边填值后，直接读取这边配置的概率</t>
         </r>
       </text>
     </comment>
@@ -81,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -115,19 +119,13 @@
     <t>升星所需碎片</t>
   </si>
   <si>
-    <t>基础停留时长加成系数</t>
+    <t>服务能力加成系数</t>
   </si>
   <si>
-    <t>额外材料掉落</t>
-  </si>
-  <si>
-    <t>备注</t>
+    <t>概率</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -145,25 +143,10 @@
     <t>Additioncoefficient</t>
   </si>
   <si>
-    <t>BonusRate</t>
+    <t>Probability</t>
   </si>
   <si>
     <t>普通路人1</t>
-  </si>
-  <si>
-    <t>0_1980000_20000</t>
-  </si>
-  <si>
-    <t>5_1980000_20000</t>
-  </si>
-  <si>
-    <t>8_1980000_20000</t>
-  </si>
-  <si>
-    <t>10_1980000_20000</t>
-  </si>
-  <si>
-    <t>15_1980000_20000</t>
   </si>
   <si>
     <t>普通路人2</t>
@@ -218,7 +201,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,12 +217,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -752,137 +729,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -898,19 +875,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,19 +1197,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H131"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
-    <col min="7" max="7" width="37.875" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:8">
+    <row r="1" ht="15.75" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,77 +1227,71 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" ht="15.75" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:8">
+    </row>
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="1"/>
-      <c r="B4" s="7"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:8">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:7">
       <c r="A5" s="1">
         <f>B5*100+D5</f>
-        <v>10101</v>
+        <v>100101</v>
       </c>
       <c r="B5" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1341,18 +1302,17 @@
       <c r="F5" s="1">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="G5" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A19" si="0">B6*100+D6</f>
-        <v>10102</v>
+        <v>100102</v>
       </c>
       <c r="B6" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2">
@@ -1364,18 +1324,17 @@
       <c r="F6" s="1">
         <v>150</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="G6" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>10103</v>
+        <v>100103</v>
       </c>
       <c r="B7" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2">
@@ -1387,18 +1346,17 @@
       <c r="F7" s="1">
         <v>200</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="G7" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>10104</v>
+        <v>100104</v>
       </c>
       <c r="B8" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
@@ -1410,18 +1368,17 @@
       <c r="F8" s="1">
         <v>250</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="G8" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>10105</v>
+        <v>100105</v>
       </c>
       <c r="B9" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2">
@@ -1433,21 +1390,20 @@
       <c r="F9" s="1">
         <v>300</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>10201</v>
+        <v>100201</v>
       </c>
       <c r="B10" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -1458,18 +1414,17 @@
       <c r="F10" s="1">
         <v>100</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="G10" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10202</v>
+        <v>100202</v>
       </c>
       <c r="B11" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2">
@@ -1481,18 +1436,17 @@
       <c r="F11" s="1">
         <v>150</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>10203</v>
+        <v>100203</v>
       </c>
       <c r="B12" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
@@ -1504,18 +1458,17 @@
       <c r="F12" s="1">
         <v>200</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="G12" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>10204</v>
+        <v>100204</v>
       </c>
       <c r="B13" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
@@ -1527,18 +1480,17 @@
       <c r="F13" s="1">
         <v>250</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="G13" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>10205</v>
+        <v>100205</v>
       </c>
       <c r="B14" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
@@ -1550,21 +1502,20 @@
       <c r="F14" s="1">
         <v>300</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="G14" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>10301</v>
+        <v>100301</v>
       </c>
       <c r="B15" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1575,18 +1526,17 @@
       <c r="F15" s="1">
         <v>100</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="G15" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>10302</v>
+        <v>100302</v>
       </c>
       <c r="B16" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2">
@@ -1598,18 +1548,17 @@
       <c r="F16" s="1">
         <v>150</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="G16" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>10303</v>
+        <v>100303</v>
       </c>
       <c r="B17" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2">
@@ -1621,18 +1570,17 @@
       <c r="F17" s="1">
         <v>200</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="G17" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>10304</v>
+        <v>100304</v>
       </c>
       <c r="B18" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
@@ -1644,18 +1592,17 @@
       <c r="F18" s="1">
         <v>250</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="G18" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>10305</v>
+        <v>100305</v>
       </c>
       <c r="B19" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2">
@@ -1667,21 +1614,20 @@
       <c r="F19" s="1">
         <v>300</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="G19" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <f t="shared" ref="A20:A51" si="1">B20*100+D20</f>
-        <v>20101</v>
+        <v>200101</v>
       </c>
       <c r="B20" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -1692,18 +1638,17 @@
       <c r="F20" s="1">
         <v>100</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="G20" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
-        <v>20102</v>
+        <v>200102</v>
       </c>
       <c r="B21" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2">
@@ -1715,18 +1660,17 @@
       <c r="F21" s="1">
         <v>150</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="G21" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
-        <v>20103</v>
+        <v>200103</v>
       </c>
       <c r="B22" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2">
@@ -1738,18 +1682,17 @@
       <c r="F22" s="1">
         <v>200</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="G22" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
-        <v>20104</v>
+        <v>200104</v>
       </c>
       <c r="B23" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2">
@@ -1761,18 +1704,17 @@
       <c r="F23" s="1">
         <v>250</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="G23" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
-        <v>20105</v>
+        <v>200105</v>
       </c>
       <c r="B24" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2">
@@ -1784,21 +1726,20 @@
       <c r="F24" s="1">
         <v>300</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="G24" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
-        <v>20201</v>
+        <v>200201</v>
       </c>
       <c r="B25" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -1809,18 +1750,17 @@
       <c r="F25" s="1">
         <v>100</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="G25" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
-        <v>20202</v>
+        <v>200202</v>
       </c>
       <c r="B26" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
@@ -1832,18 +1772,17 @@
       <c r="F26" s="1">
         <v>150</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="G26" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
-        <v>20203</v>
+        <v>200203</v>
       </c>
       <c r="B27" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
@@ -1855,18 +1794,17 @@
       <c r="F27" s="1">
         <v>200</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="G27" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
-        <v>20204</v>
+        <v>200204</v>
       </c>
       <c r="B28" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
@@ -1878,18 +1816,17 @@
       <c r="F28" s="1">
         <v>250</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="G28" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
-        <v>20205</v>
+        <v>200205</v>
       </c>
       <c r="B29" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
@@ -1901,21 +1838,20 @@
       <c r="F29" s="1">
         <v>300</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="G29" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
-        <v>20301</v>
+        <v>200301</v>
       </c>
       <c r="B30" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1926,18 +1862,17 @@
       <c r="F30" s="1">
         <v>100</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="G30" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
-        <v>20302</v>
+        <v>200302</v>
       </c>
       <c r="B31" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
@@ -1949,18 +1884,17 @@
       <c r="F31" s="1">
         <v>150</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="G31" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <f t="shared" si="1"/>
-        <v>20303</v>
+        <v>200303</v>
       </c>
       <c r="B32" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
@@ -1972,18 +1906,17 @@
       <c r="F32" s="1">
         <v>200</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="G32" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <f t="shared" si="1"/>
-        <v>20304</v>
+        <v>200304</v>
       </c>
       <c r="B33" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2">
@@ -1995,18 +1928,17 @@
       <c r="F33" s="1">
         <v>250</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="G33" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <f t="shared" si="1"/>
-        <v>20305</v>
+        <v>200305</v>
       </c>
       <c r="B34" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2">
@@ -2018,21 +1950,20 @@
       <c r="F34" s="1">
         <v>300</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="G34" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <f t="shared" si="1"/>
-        <v>30101</v>
+        <v>300101</v>
       </c>
       <c r="B35" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2043,18 +1974,17 @@
       <c r="F35" s="1">
         <v>100</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="G35" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
-        <v>30102</v>
+        <v>300102</v>
       </c>
       <c r="B36" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
@@ -2066,18 +1996,17 @@
       <c r="F36" s="1">
         <v>150</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="G36" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <f t="shared" si="1"/>
-        <v>30103</v>
+        <v>300103</v>
       </c>
       <c r="B37" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2">
@@ -2089,18 +2018,17 @@
       <c r="F37" s="1">
         <v>200</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="G37" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <f t="shared" si="1"/>
-        <v>30104</v>
+        <v>300104</v>
       </c>
       <c r="B38" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
@@ -2112,18 +2040,17 @@
       <c r="F38" s="1">
         <v>250</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="G38" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <f t="shared" si="1"/>
-        <v>30105</v>
+        <v>300105</v>
       </c>
       <c r="B39" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2">
@@ -2135,21 +2062,20 @@
       <c r="F39" s="1">
         <v>300</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="1">
+        <f t="shared" si="1"/>
+        <v>300201</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3002</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="1">
-        <f t="shared" si="1"/>
-        <v>30201</v>
-      </c>
-      <c r="B40" s="1">
-        <v>302</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -2160,18 +2086,17 @@
       <c r="F40" s="1">
         <v>100</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="G40" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <f t="shared" si="1"/>
-        <v>30202</v>
+        <v>300202</v>
       </c>
       <c r="B41" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2">
@@ -2183,18 +2108,17 @@
       <c r="F41" s="1">
         <v>150</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="G41" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <f t="shared" si="1"/>
-        <v>30203</v>
+        <v>300203</v>
       </c>
       <c r="B42" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
@@ -2206,18 +2130,17 @@
       <c r="F42" s="1">
         <v>200</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="G42" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <f t="shared" si="1"/>
-        <v>30204</v>
+        <v>300204</v>
       </c>
       <c r="B43" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
@@ -2229,18 +2152,17 @@
       <c r="F43" s="1">
         <v>250</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="G43" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <f t="shared" si="1"/>
-        <v>30205</v>
+        <v>300205</v>
       </c>
       <c r="B44" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2">
@@ -2252,21 +2174,20 @@
       <c r="F44" s="1">
         <v>300</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="G44" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <f t="shared" si="1"/>
-        <v>30301</v>
+        <v>300301</v>
       </c>
       <c r="B45" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -2277,18 +2198,17 @@
       <c r="F45" s="1">
         <v>100</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="G45" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <f t="shared" si="1"/>
-        <v>30302</v>
+        <v>300302</v>
       </c>
       <c r="B46" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
@@ -2300,18 +2220,17 @@
       <c r="F46" s="1">
         <v>150</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="G46" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <f t="shared" si="1"/>
-        <v>30303</v>
+        <v>300303</v>
       </c>
       <c r="B47" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
@@ -2323,18 +2242,17 @@
       <c r="F47" s="1">
         <v>200</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="G47" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <f t="shared" si="1"/>
-        <v>30304</v>
+        <v>300304</v>
       </c>
       <c r="B48" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
@@ -2346,18 +2264,17 @@
       <c r="F48" s="1">
         <v>250</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <f t="shared" si="1"/>
-        <v>30305</v>
+        <v>300305</v>
       </c>
       <c r="B49" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
@@ -2369,21 +2286,20 @@
       <c r="F49" s="1">
         <v>300</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <f t="shared" si="1"/>
-        <v>40101</v>
+        <v>400101</v>
       </c>
       <c r="B50" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -2394,18 +2310,17 @@
       <c r="F50" s="1">
         <v>100</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <f t="shared" si="1"/>
-        <v>40102</v>
+        <v>400102</v>
       </c>
       <c r="B51" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
@@ -2417,18 +2332,17 @@
       <c r="F51" s="1">
         <v>150</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="8"/>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="G51" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <f t="shared" ref="A52:A79" si="2">B52*100+D52</f>
-        <v>40103</v>
+        <v>400103</v>
       </c>
       <c r="B52" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
@@ -2440,18 +2354,17 @@
       <c r="F52" s="1">
         <v>200</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="G52" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <f t="shared" si="2"/>
-        <v>40104</v>
+        <v>400104</v>
       </c>
       <c r="B53" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
@@ -2463,18 +2376,17 @@
       <c r="F53" s="1">
         <v>250</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="8"/>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="G53" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <f t="shared" si="2"/>
-        <v>40105</v>
+        <v>400105</v>
       </c>
       <c r="B54" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
@@ -2486,21 +2398,20 @@
       <c r="F54" s="1">
         <v>300</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="8"/>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="G54" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <f t="shared" si="2"/>
-        <v>40201</v>
+        <v>400201</v>
       </c>
       <c r="B55" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -2511,18 +2422,17 @@
       <c r="F55" s="1">
         <v>100</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="8"/>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="G55" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <f t="shared" si="2"/>
-        <v>40202</v>
+        <v>400202</v>
       </c>
       <c r="B56" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
@@ -2534,18 +2444,17 @@
       <c r="F56" s="1">
         <v>150</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="8"/>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="G56" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
-        <v>40203</v>
+        <v>400203</v>
       </c>
       <c r="B57" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
@@ -2557,18 +2466,17 @@
       <c r="F57" s="1">
         <v>200</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="G57" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
-        <v>40204</v>
+        <v>400204</v>
       </c>
       <c r="B58" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
@@ -2580,18 +2488,17 @@
       <c r="F58" s="1">
         <v>250</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="G58" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
-        <v>40205</v>
+        <v>400205</v>
       </c>
       <c r="B59" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
@@ -2603,21 +2510,20 @@
       <c r="F59" s="1">
         <v>300</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="8"/>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="G59" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
-        <v>40301</v>
+        <v>400301</v>
       </c>
       <c r="B60" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D60" s="2">
         <v>1</v>
@@ -2628,18 +2534,17 @@
       <c r="F60" s="1">
         <v>100</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="8"/>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="G60" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <f t="shared" si="2"/>
-        <v>40302</v>
+        <v>400302</v>
       </c>
       <c r="B61" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
@@ -2651,18 +2556,17 @@
       <c r="F61" s="1">
         <v>150</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="8"/>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="G61" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <f t="shared" si="2"/>
-        <v>40303</v>
+        <v>400303</v>
       </c>
       <c r="B62" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
@@ -2674,18 +2578,17 @@
       <c r="F62" s="1">
         <v>200</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="8"/>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="G62" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1">
         <f t="shared" si="2"/>
-        <v>40304</v>
+        <v>400304</v>
       </c>
       <c r="B63" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
@@ -2697,18 +2600,17 @@
       <c r="F63" s="1">
         <v>250</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="8"/>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="G63" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="1">
         <f t="shared" si="2"/>
-        <v>40305</v>
+        <v>400305</v>
       </c>
       <c r="B64" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2">
@@ -2720,21 +2622,20 @@
       <c r="F64" s="1">
         <v>300</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" s="8"/>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="G64" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <f t="shared" si="2"/>
-        <v>50101</v>
+        <v>500101</v>
       </c>
       <c r="B65" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D65" s="2">
         <v>1</v>
@@ -2745,18 +2646,17 @@
       <c r="F65" s="1">
         <v>100</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H65" s="8"/>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="G65" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <f t="shared" si="2"/>
-        <v>50102</v>
+        <v>500102</v>
       </c>
       <c r="B66" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2">
@@ -2768,18 +2668,17 @@
       <c r="F66" s="1">
         <v>150</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H66" s="8"/>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="G66" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <f t="shared" si="2"/>
-        <v>50103</v>
+        <v>500103</v>
       </c>
       <c r="B67" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
@@ -2791,18 +2690,17 @@
       <c r="F67" s="1">
         <v>200</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H67" s="8"/>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="G67" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="1">
         <f t="shared" si="2"/>
-        <v>50104</v>
+        <v>500104</v>
       </c>
       <c r="B68" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
@@ -2814,18 +2712,17 @@
       <c r="F68" s="1">
         <v>250</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="8"/>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="G68" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1">
         <f t="shared" si="2"/>
-        <v>50105</v>
+        <v>500105</v>
       </c>
       <c r="B69" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
@@ -2837,21 +2734,20 @@
       <c r="F69" s="1">
         <v>300</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="8"/>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="G69" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="1">
         <f t="shared" si="2"/>
-        <v>50201</v>
+        <v>500201</v>
       </c>
       <c r="B70" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D70" s="2">
         <v>1</v>
@@ -2862,18 +2758,17 @@
       <c r="F70" s="1">
         <v>100</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" s="8"/>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="G70" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="1">
         <f t="shared" si="2"/>
-        <v>50202</v>
+        <v>500202</v>
       </c>
       <c r="B71" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
@@ -2885,18 +2780,17 @@
       <c r="F71" s="1">
         <v>150</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="8"/>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="G71" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="1">
         <f t="shared" si="2"/>
-        <v>50203</v>
+        <v>500203</v>
       </c>
       <c r="B72" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
@@ -2908,18 +2802,17 @@
       <c r="F72" s="1">
         <v>200</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" s="8"/>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="G72" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="1">
         <f t="shared" si="2"/>
-        <v>50204</v>
+        <v>500204</v>
       </c>
       <c r="B73" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
@@ -2931,18 +2824,17 @@
       <c r="F73" s="1">
         <v>250</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="8"/>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="G73" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="1">
         <f t="shared" si="2"/>
-        <v>50205</v>
+        <v>500205</v>
       </c>
       <c r="B74" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2">
@@ -2954,21 +2846,20 @@
       <c r="F74" s="1">
         <v>300</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" s="8"/>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="G74" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="1">
         <f t="shared" si="2"/>
-        <v>50301</v>
+        <v>500301</v>
       </c>
       <c r="B75" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -2979,18 +2870,17 @@
       <c r="F75" s="1">
         <v>100</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H75" s="8"/>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="G75" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="1">
         <f t="shared" si="2"/>
-        <v>50302</v>
+        <v>500302</v>
       </c>
       <c r="B76" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2">
@@ -3002,18 +2892,17 @@
       <c r="F76" s="1">
         <v>150</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" s="8"/>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="G76" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" s="1">
         <f t="shared" si="2"/>
-        <v>50303</v>
+        <v>500303</v>
       </c>
       <c r="B77" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2">
@@ -3025,18 +2914,17 @@
       <c r="F77" s="1">
         <v>200</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H77" s="8"/>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="G77" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="1">
         <f t="shared" si="2"/>
-        <v>50304</v>
+        <v>500304</v>
       </c>
       <c r="B78" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2">
@@ -3048,18 +2936,17 @@
       <c r="F78" s="1">
         <v>250</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="8"/>
-    </row>
-    <row r="79" spans="1:8">
+      <c r="G78" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="1">
         <f t="shared" si="2"/>
-        <v>50305</v>
+        <v>500305</v>
       </c>
       <c r="B79" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2">
@@ -3071,19 +2958,18 @@
       <c r="F79" s="1">
         <v>300</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H79" s="8"/>
+      <c r="G79" s="1">
+        <v>6000</v>
+      </c>
     </row>
     <row r="114" ht="14.25" spans="5:5">
-      <c r="E114" s="9"/>
+      <c r="E114" s="6"/>
     </row>
     <row r="130" ht="14.25" spans="5:5">
-      <c r="E130" s="9"/>
+      <c r="E130" s="6"/>
     </row>
     <row r="131" ht="14.25" spans="5:5">
-      <c r="E131" s="9"/>
+      <c r="E131" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -146,49 +146,94 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>普通路人1</t>
+    <t>街头潮人</t>
   </si>
   <si>
-    <t>普通路人2</t>
+    <t>复古绅士</t>
   </si>
   <si>
-    <t>普通路人3</t>
+    <t>酷盖少年</t>
   </si>
   <si>
-    <t>精英白领1</t>
+    <t>文艺青年</t>
   </si>
   <si>
-    <t>精英白领2</t>
+    <t>书香少女</t>
   </si>
   <si>
-    <t>精英白领3</t>
+    <t>民谣歌手</t>
   </si>
   <si>
-    <t>社交名流1</t>
+    <t>潮流先锋</t>
   </si>
   <si>
-    <t>社交名流2</t>
+    <t>时尚教主</t>
   </si>
   <si>
-    <t>社交名流3</t>
+    <t>街拍达人</t>
   </si>
   <si>
-    <t>富豪商人1</t>
+    <t>马拉松客</t>
   </si>
   <si>
-    <t>富豪商人2</t>
+    <t>极限玩家</t>
   </si>
   <si>
-    <t>富豪商人3</t>
+    <t>科技极客</t>
   </si>
   <si>
-    <t>达官显贵1</t>
+    <t>运动健将</t>
   </si>
   <si>
-    <t>达官显贵2</t>
+    <t>跑酷少年</t>
   </si>
   <si>
-    <t>达官显贵3</t>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
+    <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>古典乐迷</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>高定女王</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1620,13 +1665,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A51" si="1">B20*100+D20</f>
-        <v>200101</v>
+        <f t="shared" ref="A20:A34" si="1">B20*100+D20</f>
+        <v>100401</v>
       </c>
       <c r="B20" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C20" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="2">
@@ -1645,12 +1690,12 @@
     <row r="21" spans="1:7">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
-        <v>200102</v>
+        <v>100402</v>
       </c>
       <c r="B21" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="2">
         <v>2</v>
       </c>
@@ -1667,12 +1712,12 @@
     <row r="22" spans="1:7">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
-        <v>200103</v>
+        <v>100403</v>
       </c>
       <c r="B22" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="2">
         <v>3</v>
       </c>
@@ -1689,12 +1734,12 @@
     <row r="23" spans="1:7">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
-        <v>200104</v>
+        <v>100404</v>
       </c>
       <c r="B23" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="C23" s="1"/>
       <c r="D23" s="2">
         <v>4</v>
       </c>
@@ -1711,12 +1756,12 @@
     <row r="24" spans="1:7">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
-        <v>200105</v>
+        <v>100405</v>
       </c>
       <c r="B24" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="C24" s="1"/>
       <c r="D24" s="2">
         <v>5</v>
       </c>
@@ -1733,12 +1778,12 @@
     <row r="25" spans="1:7">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
-        <v>200201</v>
+        <v>100501</v>
       </c>
       <c r="B25" s="1">
-        <v>2002</v>
-      </c>
-      <c r="C25" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="2">
@@ -1757,12 +1802,12 @@
     <row r="26" spans="1:7">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
-        <v>200202</v>
+        <v>100502</v>
       </c>
       <c r="B26" s="1">
-        <v>2002</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>1005</v>
+      </c>
+      <c r="C26" s="1"/>
       <c r="D26" s="2">
         <v>2</v>
       </c>
@@ -1779,12 +1824,12 @@
     <row r="27" spans="1:7">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
-        <v>200203</v>
+        <v>100503</v>
       </c>
       <c r="B27" s="1">
-        <v>2002</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>1005</v>
+      </c>
+      <c r="C27" s="1"/>
       <c r="D27" s="2">
         <v>3</v>
       </c>
@@ -1801,12 +1846,12 @@
     <row r="28" spans="1:7">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
-        <v>200204</v>
+        <v>100504</v>
       </c>
       <c r="B28" s="1">
-        <v>2002</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>1005</v>
+      </c>
+      <c r="C28" s="1"/>
       <c r="D28" s="2">
         <v>4</v>
       </c>
@@ -1823,12 +1868,12 @@
     <row r="29" spans="1:7">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
-        <v>200205</v>
+        <v>100505</v>
       </c>
       <c r="B29" s="1">
-        <v>2002</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>1005</v>
+      </c>
+      <c r="C29" s="1"/>
       <c r="D29" s="2">
         <v>5</v>
       </c>
@@ -1845,12 +1890,12 @@
     <row r="30" spans="1:7">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
-        <v>200301</v>
+        <v>100601</v>
       </c>
       <c r="B30" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C30" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="2">
@@ -1869,12 +1914,12 @@
     <row r="31" spans="1:7">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
-        <v>200302</v>
+        <v>100602</v>
       </c>
       <c r="B31" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="C31" s="1"/>
       <c r="D31" s="2">
         <v>2</v>
       </c>
@@ -1891,12 +1936,12 @@
     <row r="32" spans="1:7">
       <c r="A32" s="1">
         <f t="shared" si="1"/>
-        <v>200303</v>
+        <v>100603</v>
       </c>
       <c r="B32" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="C32" s="1"/>
       <c r="D32" s="2">
         <v>3</v>
       </c>
@@ -1913,12 +1958,12 @@
     <row r="33" spans="1:7">
       <c r="A33" s="1">
         <f t="shared" si="1"/>
-        <v>200304</v>
+        <v>100604</v>
       </c>
       <c r="B33" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="C33" s="1"/>
       <c r="D33" s="2">
         <v>4</v>
       </c>
@@ -1935,12 +1980,12 @@
     <row r="34" spans="1:7">
       <c r="A34" s="1">
         <f t="shared" si="1"/>
-        <v>200305</v>
+        <v>100605</v>
       </c>
       <c r="B34" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="C34" s="1"/>
       <c r="D34" s="2">
         <v>5</v>
       </c>
@@ -1956,13 +2001,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
-        <v>300101</v>
+        <f>B35*100+D35</f>
+        <v>200101</v>
       </c>
       <c r="B35" s="1">
-        <v>3001</v>
-      </c>
-      <c r="C35" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="2">
@@ -1980,11 +2025,11 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <f t="shared" si="1"/>
-        <v>300102</v>
+        <f>B36*100+D36</f>
+        <v>200102</v>
       </c>
       <c r="B36" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
@@ -2002,11 +2047,11 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <f t="shared" si="1"/>
-        <v>300103</v>
+        <f>B37*100+D37</f>
+        <v>200103</v>
       </c>
       <c r="B37" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2">
@@ -2024,11 +2069,11 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <f t="shared" si="1"/>
-        <v>300104</v>
+        <f>B38*100+D38</f>
+        <v>200104</v>
       </c>
       <c r="B38" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
@@ -2046,11 +2091,11 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <f t="shared" si="1"/>
-        <v>300105</v>
+        <f>B39*100+D39</f>
+        <v>200105</v>
       </c>
       <c r="B39" s="1">
-        <v>3001</v>
+        <v>2001</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2">
@@ -2068,13 +2113,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <f t="shared" si="1"/>
-        <v>300201</v>
+        <f>B40*100+D40</f>
+        <v>200201</v>
       </c>
       <c r="B40" s="1">
-        <v>3002</v>
-      </c>
-      <c r="C40" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="2">
@@ -2092,11 +2137,11 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <f t="shared" si="1"/>
-        <v>300202</v>
+        <f>B41*100+D41</f>
+        <v>200202</v>
       </c>
       <c r="B41" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2">
@@ -2114,11 +2159,11 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <f t="shared" si="1"/>
-        <v>300203</v>
+        <f>B42*100+D42</f>
+        <v>200203</v>
       </c>
       <c r="B42" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
@@ -2136,11 +2181,11 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <f t="shared" si="1"/>
-        <v>300204</v>
+        <f>B43*100+D43</f>
+        <v>200204</v>
       </c>
       <c r="B43" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
@@ -2158,11 +2203,11 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <f t="shared" si="1"/>
-        <v>300205</v>
+        <f>B44*100+D44</f>
+        <v>200205</v>
       </c>
       <c r="B44" s="1">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2">
@@ -2180,13 +2225,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <f t="shared" si="1"/>
-        <v>300301</v>
+        <f>B45*100+D45</f>
+        <v>200301</v>
       </c>
       <c r="B45" s="1">
-        <v>3003</v>
-      </c>
-      <c r="C45" s="1" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="2">
@@ -2204,11 +2249,11 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <f t="shared" si="1"/>
-        <v>300302</v>
+        <f>B46*100+D46</f>
+        <v>200302</v>
       </c>
       <c r="B46" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
@@ -2226,11 +2271,11 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <f t="shared" si="1"/>
-        <v>300303</v>
+        <f>B47*100+D47</f>
+        <v>200303</v>
       </c>
       <c r="B47" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
@@ -2248,11 +2293,11 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <f t="shared" si="1"/>
-        <v>300304</v>
+        <f>B48*100+D48</f>
+        <v>200304</v>
       </c>
       <c r="B48" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
@@ -2270,11 +2315,11 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <f t="shared" si="1"/>
-        <v>300305</v>
+        <f>B49*100+D49</f>
+        <v>200305</v>
       </c>
       <c r="B49" s="1">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
@@ -2292,13 +2337,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <f t="shared" si="1"/>
-        <v>400101</v>
+        <f t="shared" ref="A50:A64" si="2">B50*100+D50</f>
+        <v>200401</v>
       </c>
       <c r="B50" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C50" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="2">
@@ -2316,13 +2361,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <f t="shared" si="1"/>
-        <v>400102</v>
+        <f t="shared" si="2"/>
+        <v>200402</v>
       </c>
       <c r="B51" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>2004</v>
+      </c>
+      <c r="C51" s="1"/>
       <c r="D51" s="2">
         <v>2</v>
       </c>
@@ -2338,13 +2383,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <f t="shared" ref="A52:A79" si="2">B52*100+D52</f>
-        <v>400103</v>
+        <f t="shared" si="2"/>
+        <v>200403</v>
       </c>
       <c r="B52" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>2004</v>
+      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="2">
         <v>3</v>
       </c>
@@ -2361,12 +2406,12 @@
     <row r="53" spans="1:7">
       <c r="A53" s="1">
         <f t="shared" si="2"/>
-        <v>400104</v>
+        <v>200404</v>
       </c>
       <c r="B53" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>2004</v>
+      </c>
+      <c r="C53" s="1"/>
       <c r="D53" s="2">
         <v>4</v>
       </c>
@@ -2383,12 +2428,12 @@
     <row r="54" spans="1:7">
       <c r="A54" s="1">
         <f t="shared" si="2"/>
-        <v>400105</v>
+        <v>200405</v>
       </c>
       <c r="B54" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>2004</v>
+      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="2">
         <v>5</v>
       </c>
@@ -2405,12 +2450,12 @@
     <row r="55" spans="1:7">
       <c r="A55" s="1">
         <f t="shared" si="2"/>
-        <v>400201</v>
+        <v>200501</v>
       </c>
       <c r="B55" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C55" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D55" s="2">
@@ -2429,12 +2474,12 @@
     <row r="56" spans="1:7">
       <c r="A56" s="1">
         <f t="shared" si="2"/>
-        <v>400202</v>
+        <v>200502</v>
       </c>
       <c r="B56" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>2005</v>
+      </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="2">
         <v>2</v>
       </c>
@@ -2451,12 +2496,12 @@
     <row r="57" spans="1:7">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
-        <v>400203</v>
+        <v>200503</v>
       </c>
       <c r="B57" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>2005</v>
+      </c>
+      <c r="C57" s="1"/>
       <c r="D57" s="2">
         <v>3</v>
       </c>
@@ -2473,12 +2518,12 @@
     <row r="58" spans="1:7">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
-        <v>400204</v>
+        <v>200504</v>
       </c>
       <c r="B58" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>2005</v>
+      </c>
+      <c r="C58" s="1"/>
       <c r="D58" s="2">
         <v>4</v>
       </c>
@@ -2495,12 +2540,12 @@
     <row r="59" spans="1:7">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
-        <v>400205</v>
+        <v>200505</v>
       </c>
       <c r="B59" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>2005</v>
+      </c>
+      <c r="C59" s="1"/>
       <c r="D59" s="2">
         <v>5</v>
       </c>
@@ -2517,12 +2562,12 @@
     <row r="60" spans="1:7">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
-        <v>400301</v>
+        <v>200601</v>
       </c>
       <c r="B60" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C60" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2">
@@ -2541,12 +2586,12 @@
     <row r="61" spans="1:7">
       <c r="A61" s="1">
         <f t="shared" si="2"/>
-        <v>400302</v>
+        <v>200602</v>
       </c>
       <c r="B61" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>2006</v>
+      </c>
+      <c r="C61" s="1"/>
       <c r="D61" s="2">
         <v>2</v>
       </c>
@@ -2563,12 +2608,12 @@
     <row r="62" spans="1:7">
       <c r="A62" s="1">
         <f t="shared" si="2"/>
-        <v>400303</v>
+        <v>200603</v>
       </c>
       <c r="B62" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>2006</v>
+      </c>
+      <c r="C62" s="1"/>
       <c r="D62" s="2">
         <v>3</v>
       </c>
@@ -2585,12 +2630,12 @@
     <row r="63" spans="1:7">
       <c r="A63" s="1">
         <f t="shared" si="2"/>
-        <v>400304</v>
+        <v>200604</v>
       </c>
       <c r="B63" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>2006</v>
+      </c>
+      <c r="C63" s="1"/>
       <c r="D63" s="2">
         <v>4</v>
       </c>
@@ -2607,12 +2652,12 @@
     <row r="64" spans="1:7">
       <c r="A64" s="1">
         <f t="shared" si="2"/>
-        <v>400305</v>
+        <v>200605</v>
       </c>
       <c r="B64" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>2006</v>
+      </c>
+      <c r="C64" s="1"/>
       <c r="D64" s="2">
         <v>5</v>
       </c>
@@ -2628,13 +2673,13 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <f t="shared" si="2"/>
-        <v>500101</v>
+        <f t="shared" ref="A65:A81" si="3">B65*100+D65</f>
+        <v>300101</v>
       </c>
       <c r="B65" s="1">
-        <v>5001</v>
-      </c>
-      <c r="C65" s="1" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D65" s="2">
@@ -2652,11 +2697,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <f t="shared" si="2"/>
-        <v>500102</v>
+        <f t="shared" si="3"/>
+        <v>300102</v>
       </c>
       <c r="B66" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2">
@@ -2674,11 +2719,11 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <f t="shared" si="2"/>
-        <v>500103</v>
+        <f t="shared" si="3"/>
+        <v>300103</v>
       </c>
       <c r="B67" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
@@ -2696,11 +2741,11 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <f t="shared" si="2"/>
-        <v>500104</v>
+        <f t="shared" si="3"/>
+        <v>300104</v>
       </c>
       <c r="B68" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
@@ -2718,11 +2763,11 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <f t="shared" si="2"/>
-        <v>500105</v>
+        <f t="shared" si="3"/>
+        <v>300105</v>
       </c>
       <c r="B69" s="1">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
@@ -2740,13 +2785,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <f t="shared" si="2"/>
-        <v>500201</v>
+        <f t="shared" si="3"/>
+        <v>300201</v>
       </c>
       <c r="B70" s="1">
-        <v>5002</v>
-      </c>
-      <c r="C70" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D70" s="2">
@@ -2764,11 +2809,11 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <f t="shared" si="2"/>
-        <v>500202</v>
+        <f t="shared" si="3"/>
+        <v>300202</v>
       </c>
       <c r="B71" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
@@ -2786,11 +2831,11 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <f t="shared" si="2"/>
-        <v>500203</v>
+        <f t="shared" si="3"/>
+        <v>300203</v>
       </c>
       <c r="B72" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
@@ -2808,11 +2853,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <f t="shared" si="2"/>
-        <v>500204</v>
+        <f t="shared" si="3"/>
+        <v>300204</v>
       </c>
       <c r="B73" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
@@ -2830,11 +2875,11 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
-        <f t="shared" si="2"/>
-        <v>500205</v>
+        <f t="shared" si="3"/>
+        <v>300205</v>
       </c>
       <c r="B74" s="1">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2">
@@ -2852,13 +2897,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
-        <f t="shared" si="2"/>
-        <v>500301</v>
+        <f t="shared" si="3"/>
+        <v>300301</v>
       </c>
       <c r="B75" s="1">
-        <v>5003</v>
-      </c>
-      <c r="C75" s="1" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="2">
@@ -2876,11 +2921,11 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
-        <f t="shared" si="2"/>
-        <v>500302</v>
+        <f t="shared" si="3"/>
+        <v>300302</v>
       </c>
       <c r="B76" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2">
@@ -2898,11 +2943,11 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1">
-        <f t="shared" si="2"/>
-        <v>500303</v>
+        <f t="shared" si="3"/>
+        <v>300303</v>
       </c>
       <c r="B77" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2">
@@ -2920,11 +2965,11 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="1">
-        <f t="shared" si="2"/>
-        <v>500304</v>
+        <f t="shared" si="3"/>
+        <v>300304</v>
       </c>
       <c r="B78" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2">
@@ -2942,11 +2987,11 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1">
-        <f t="shared" si="2"/>
-        <v>500305</v>
+        <f t="shared" si="3"/>
+        <v>300305</v>
       </c>
       <c r="B79" s="1">
-        <v>5003</v>
+        <v>3003</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2">
@@ -2962,14 +3007,1694 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="114" ht="14.25" spans="5:5">
-      <c r="E114" s="6"/>
-    </row>
-    <row r="130" ht="14.25" spans="5:5">
-      <c r="E130" s="6"/>
-    </row>
-    <row r="131" ht="14.25" spans="5:5">
-      <c r="E131" s="6"/>
+    <row r="80" spans="1:7">
+      <c r="A80" s="1">
+        <f t="shared" ref="A80:A94" si="4">B80*100+D80</f>
+        <v>300401</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" s="2">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="1">
+        <v>100</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="1">
+        <f t="shared" si="4"/>
+        <v>300402</v>
+      </c>
+      <c r="B81" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="1">
+        <v>10</v>
+      </c>
+      <c r="F81" s="1">
+        <v>150</v>
+      </c>
+      <c r="G81" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="1">
+        <f t="shared" si="4"/>
+        <v>300403</v>
+      </c>
+      <c r="B82" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="2">
+        <v>3</v>
+      </c>
+      <c r="E82" s="1">
+        <v>15</v>
+      </c>
+      <c r="F82" s="1">
+        <v>200</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="1">
+        <f t="shared" si="4"/>
+        <v>300404</v>
+      </c>
+      <c r="B83" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="2">
+        <v>4</v>
+      </c>
+      <c r="E83" s="1">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1">
+        <v>250</v>
+      </c>
+      <c r="G83" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1">
+        <f t="shared" si="4"/>
+        <v>300405</v>
+      </c>
+      <c r="B84" s="1">
+        <v>3004</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="2">
+        <v>5</v>
+      </c>
+      <c r="E84" s="1">
+        <v>25</v>
+      </c>
+      <c r="F84" s="1">
+        <v>300</v>
+      </c>
+      <c r="G84" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="1">
+        <f t="shared" si="4"/>
+        <v>300501</v>
+      </c>
+      <c r="B85" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <v>100</v>
+      </c>
+      <c r="G85" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="1">
+        <f t="shared" si="4"/>
+        <v>300502</v>
+      </c>
+      <c r="B86" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="2">
+        <v>2</v>
+      </c>
+      <c r="E86" s="1">
+        <v>10</v>
+      </c>
+      <c r="F86" s="1">
+        <v>150</v>
+      </c>
+      <c r="G86" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="1">
+        <f t="shared" si="4"/>
+        <v>300503</v>
+      </c>
+      <c r="B87" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="2">
+        <v>3</v>
+      </c>
+      <c r="E87" s="1">
+        <v>15</v>
+      </c>
+      <c r="F87" s="1">
+        <v>200</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="1">
+        <f t="shared" si="4"/>
+        <v>300504</v>
+      </c>
+      <c r="B88" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="2">
+        <v>4</v>
+      </c>
+      <c r="E88" s="1">
+        <v>20</v>
+      </c>
+      <c r="F88" s="1">
+        <v>250</v>
+      </c>
+      <c r="G88" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="1">
+        <f t="shared" si="4"/>
+        <v>300505</v>
+      </c>
+      <c r="B89" s="1">
+        <v>3005</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="2">
+        <v>5</v>
+      </c>
+      <c r="E89" s="1">
+        <v>25</v>
+      </c>
+      <c r="F89" s="1">
+        <v>300</v>
+      </c>
+      <c r="G89" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="1">
+        <f t="shared" si="4"/>
+        <v>300601</v>
+      </c>
+      <c r="B90" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
+        <v>100</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="1">
+        <f t="shared" si="4"/>
+        <v>300602</v>
+      </c>
+      <c r="B91" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="1">
+        <v>10</v>
+      </c>
+      <c r="F91" s="1">
+        <v>150</v>
+      </c>
+      <c r="G91" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="1">
+        <f t="shared" si="4"/>
+        <v>300603</v>
+      </c>
+      <c r="B92" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="2">
+        <v>3</v>
+      </c>
+      <c r="E92" s="1">
+        <v>15</v>
+      </c>
+      <c r="F92" s="1">
+        <v>200</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="1">
+        <f t="shared" si="4"/>
+        <v>300604</v>
+      </c>
+      <c r="B93" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="2">
+        <v>4</v>
+      </c>
+      <c r="E93" s="1">
+        <v>20</v>
+      </c>
+      <c r="F93" s="1">
+        <v>250</v>
+      </c>
+      <c r="G93" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="1">
+        <f t="shared" si="4"/>
+        <v>300605</v>
+      </c>
+      <c r="B94" s="1">
+        <v>3006</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="2">
+        <v>5</v>
+      </c>
+      <c r="E94" s="1">
+        <v>25</v>
+      </c>
+      <c r="F94" s="1">
+        <v>300</v>
+      </c>
+      <c r="G94" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="1">
+        <f>B95*100+D95</f>
+        <v>400101</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1">
+        <v>100</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="1">
+        <f>B96*100+D96</f>
+        <v>400102</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="1">
+        <v>10</v>
+      </c>
+      <c r="F96" s="1">
+        <v>150</v>
+      </c>
+      <c r="G96" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="1">
+        <f>B97*100+D97</f>
+        <v>400103</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2">
+        <v>3</v>
+      </c>
+      <c r="E97" s="1">
+        <v>15</v>
+      </c>
+      <c r="F97" s="1">
+        <v>200</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="1">
+        <f>B98*100+D98</f>
+        <v>400104</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1">
+        <v>20</v>
+      </c>
+      <c r="F98" s="1">
+        <v>250</v>
+      </c>
+      <c r="G98" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="1">
+        <f>B99*100+D99</f>
+        <v>400105</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2">
+        <v>5</v>
+      </c>
+      <c r="E99" s="1">
+        <v>25</v>
+      </c>
+      <c r="F99" s="1">
+        <v>300</v>
+      </c>
+      <c r="G99" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="1">
+        <f>B100*100+D100</f>
+        <v>400201</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1">
+        <v>100</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="1">
+        <f>B101*100+D101</f>
+        <v>400202</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2">
+        <v>2</v>
+      </c>
+      <c r="E101" s="1">
+        <v>10</v>
+      </c>
+      <c r="F101" s="1">
+        <v>150</v>
+      </c>
+      <c r="G101" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="1">
+        <f>B102*100+D102</f>
+        <v>400203</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2">
+        <v>3</v>
+      </c>
+      <c r="E102" s="1">
+        <v>15</v>
+      </c>
+      <c r="F102" s="1">
+        <v>200</v>
+      </c>
+      <c r="G102" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="1">
+        <f>B103*100+D103</f>
+        <v>400204</v>
+      </c>
+      <c r="B103" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>20</v>
+      </c>
+      <c r="F103" s="1">
+        <v>250</v>
+      </c>
+      <c r="G103" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="1">
+        <f>B104*100+D104</f>
+        <v>400205</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2">
+        <v>5</v>
+      </c>
+      <c r="E104" s="1">
+        <v>25</v>
+      </c>
+      <c r="F104" s="1">
+        <v>300</v>
+      </c>
+      <c r="G104" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="1">
+        <f>B105*100+D105</f>
+        <v>400301</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="2">
+        <v>1</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1">
+        <v>100</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="1">
+        <f>B106*100+D106</f>
+        <v>400302</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="1">
+        <v>10</v>
+      </c>
+      <c r="F106" s="1">
+        <v>150</v>
+      </c>
+      <c r="G106" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="1">
+        <f>B107*100+D107</f>
+        <v>400303</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2">
+        <v>3</v>
+      </c>
+      <c r="E107" s="1">
+        <v>15</v>
+      </c>
+      <c r="F107" s="1">
+        <v>200</v>
+      </c>
+      <c r="G107" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="1">
+        <f>B108*100+D108</f>
+        <v>400304</v>
+      </c>
+      <c r="B108" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2">
+        <v>4</v>
+      </c>
+      <c r="E108" s="1">
+        <v>20</v>
+      </c>
+      <c r="F108" s="1">
+        <v>250</v>
+      </c>
+      <c r="G108" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="1">
+        <f>B109*100+D109</f>
+        <v>400305</v>
+      </c>
+      <c r="B109" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>25</v>
+      </c>
+      <c r="F109" s="1">
+        <v>300</v>
+      </c>
+      <c r="G109" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="1">
+        <f t="shared" ref="A110:A124" si="5">B110*100+D110</f>
+        <v>400401</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D110" s="2">
+        <v>1</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
+        <v>100</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="1">
+        <f t="shared" si="5"/>
+        <v>400402</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="D111" s="2">
+        <v>2</v>
+      </c>
+      <c r="E111" s="1">
+        <v>10</v>
+      </c>
+      <c r="F111" s="1">
+        <v>150</v>
+      </c>
+      <c r="G111" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="1">
+        <f t="shared" si="5"/>
+        <v>400403</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C112" s="1"/>
+      <c r="D112" s="2">
+        <v>3</v>
+      </c>
+      <c r="E112" s="1">
+        <v>15</v>
+      </c>
+      <c r="F112" s="1">
+        <v>200</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="1">
+        <f t="shared" si="5"/>
+        <v>400404</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="D113" s="2">
+        <v>4</v>
+      </c>
+      <c r="E113" s="1">
+        <v>20</v>
+      </c>
+      <c r="F113" s="1">
+        <v>250</v>
+      </c>
+      <c r="G113" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="1">
+        <f t="shared" si="5"/>
+        <v>400405</v>
+      </c>
+      <c r="B114" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="D114" s="2">
+        <v>5</v>
+      </c>
+      <c r="E114" s="1">
+        <v>25</v>
+      </c>
+      <c r="F114" s="1">
+        <v>300</v>
+      </c>
+      <c r="G114" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="1">
+        <f t="shared" si="5"/>
+        <v>400501</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1">
+        <v>100</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="1">
+        <f t="shared" si="5"/>
+        <v>400502</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="D116" s="2">
+        <v>2</v>
+      </c>
+      <c r="E116" s="1">
+        <v>10</v>
+      </c>
+      <c r="F116" s="1">
+        <v>150</v>
+      </c>
+      <c r="G116" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="1">
+        <f t="shared" si="5"/>
+        <v>400503</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C117" s="1"/>
+      <c r="D117" s="2">
+        <v>3</v>
+      </c>
+      <c r="E117" s="1">
+        <v>15</v>
+      </c>
+      <c r="F117" s="1">
+        <v>200</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="1">
+        <f t="shared" si="5"/>
+        <v>400504</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="D118" s="2">
+        <v>4</v>
+      </c>
+      <c r="E118" s="1">
+        <v>20</v>
+      </c>
+      <c r="F118" s="1">
+        <v>250</v>
+      </c>
+      <c r="G118" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="1">
+        <f t="shared" si="5"/>
+        <v>400505</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="D119" s="2">
+        <v>5</v>
+      </c>
+      <c r="E119" s="1">
+        <v>25</v>
+      </c>
+      <c r="F119" s="1">
+        <v>300</v>
+      </c>
+      <c r="G119" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="1">
+        <f t="shared" si="5"/>
+        <v>400601</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1">
+        <v>100</v>
+      </c>
+      <c r="G120" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="1">
+        <f t="shared" si="5"/>
+        <v>400602</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="2">
+        <v>2</v>
+      </c>
+      <c r="E121" s="1">
+        <v>10</v>
+      </c>
+      <c r="F121" s="1">
+        <v>150</v>
+      </c>
+      <c r="G121" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="1">
+        <f t="shared" si="5"/>
+        <v>400603</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="D122" s="2">
+        <v>3</v>
+      </c>
+      <c r="E122" s="1">
+        <v>15</v>
+      </c>
+      <c r="F122" s="1">
+        <v>200</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="1">
+        <f t="shared" si="5"/>
+        <v>400604</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="2">
+        <v>4</v>
+      </c>
+      <c r="E123" s="1">
+        <v>20</v>
+      </c>
+      <c r="F123" s="1">
+        <v>250</v>
+      </c>
+      <c r="G123" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="1">
+        <f t="shared" si="5"/>
+        <v>400605</v>
+      </c>
+      <c r="B124" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="2">
+        <v>5</v>
+      </c>
+      <c r="E124" s="1">
+        <v>25</v>
+      </c>
+      <c r="F124" s="1">
+        <v>300</v>
+      </c>
+      <c r="G124" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="1">
+        <f t="shared" ref="A125:A139" si="6">B125*100+D125</f>
+        <v>500101</v>
+      </c>
+      <c r="B125" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1</v>
+      </c>
+      <c r="E125" s="1">
+        <v>0</v>
+      </c>
+      <c r="F125" s="1">
+        <v>100</v>
+      </c>
+      <c r="G125" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="1">
+        <f t="shared" si="6"/>
+        <v>500102</v>
+      </c>
+      <c r="B126" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2">
+        <v>2</v>
+      </c>
+      <c r="E126" s="1">
+        <v>10</v>
+      </c>
+      <c r="F126" s="1">
+        <v>150</v>
+      </c>
+      <c r="G126" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="1">
+        <f t="shared" si="6"/>
+        <v>500103</v>
+      </c>
+      <c r="B127" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2">
+        <v>3</v>
+      </c>
+      <c r="E127" s="1">
+        <v>15</v>
+      </c>
+      <c r="F127" s="1">
+        <v>200</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="1">
+        <f t="shared" si="6"/>
+        <v>500104</v>
+      </c>
+      <c r="B128" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2">
+        <v>4</v>
+      </c>
+      <c r="E128" s="1">
+        <v>20</v>
+      </c>
+      <c r="F128" s="1">
+        <v>250</v>
+      </c>
+      <c r="G128" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="1">
+        <f t="shared" si="6"/>
+        <v>500105</v>
+      </c>
+      <c r="B129" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2">
+        <v>5</v>
+      </c>
+      <c r="E129" s="1">
+        <v>25</v>
+      </c>
+      <c r="F129" s="1">
+        <v>300</v>
+      </c>
+      <c r="G129" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="1">
+        <f t="shared" si="6"/>
+        <v>500201</v>
+      </c>
+      <c r="B130" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D130" s="2">
+        <v>1</v>
+      </c>
+      <c r="E130" s="1">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
+        <v>100</v>
+      </c>
+      <c r="G130" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="1">
+        <f t="shared" si="6"/>
+        <v>500202</v>
+      </c>
+      <c r="B131" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2">
+        <v>2</v>
+      </c>
+      <c r="E131" s="1">
+        <v>10</v>
+      </c>
+      <c r="F131" s="1">
+        <v>150</v>
+      </c>
+      <c r="G131" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="1">
+        <f t="shared" si="6"/>
+        <v>500203</v>
+      </c>
+      <c r="B132" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2">
+        <v>3</v>
+      </c>
+      <c r="E132" s="1">
+        <v>15</v>
+      </c>
+      <c r="F132" s="1">
+        <v>200</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="1">
+        <f t="shared" si="6"/>
+        <v>500204</v>
+      </c>
+      <c r="B133" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2">
+        <v>4</v>
+      </c>
+      <c r="E133" s="1">
+        <v>20</v>
+      </c>
+      <c r="F133" s="1">
+        <v>250</v>
+      </c>
+      <c r="G133" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="1">
+        <f t="shared" si="6"/>
+        <v>500205</v>
+      </c>
+      <c r="B134" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2">
+        <v>5</v>
+      </c>
+      <c r="E134" s="1">
+        <v>25</v>
+      </c>
+      <c r="F134" s="1">
+        <v>300</v>
+      </c>
+      <c r="G134" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="1">
+        <f t="shared" si="6"/>
+        <v>500301</v>
+      </c>
+      <c r="B135" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1</v>
+      </c>
+      <c r="E135" s="1">
+        <v>0</v>
+      </c>
+      <c r="F135" s="1">
+        <v>100</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="1">
+        <f t="shared" si="6"/>
+        <v>500302</v>
+      </c>
+      <c r="B136" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2">
+        <v>2</v>
+      </c>
+      <c r="E136" s="1">
+        <v>10</v>
+      </c>
+      <c r="F136" s="1">
+        <v>150</v>
+      </c>
+      <c r="G136" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="1">
+        <f t="shared" si="6"/>
+        <v>500303</v>
+      </c>
+      <c r="B137" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2">
+        <v>3</v>
+      </c>
+      <c r="E137" s="1">
+        <v>15</v>
+      </c>
+      <c r="F137" s="1">
+        <v>200</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="1">
+        <f t="shared" si="6"/>
+        <v>500304</v>
+      </c>
+      <c r="B138" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2">
+        <v>4</v>
+      </c>
+      <c r="E138" s="1">
+        <v>20</v>
+      </c>
+      <c r="F138" s="1">
+        <v>250</v>
+      </c>
+      <c r="G138" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="1">
+        <f t="shared" si="6"/>
+        <v>500305</v>
+      </c>
+      <c r="B139" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2">
+        <v>5</v>
+      </c>
+      <c r="E139" s="1">
+        <v>25</v>
+      </c>
+      <c r="F139" s="1">
+        <v>300</v>
+      </c>
+      <c r="G139" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="1">
+        <f t="shared" ref="A140:A154" si="7">B140*100+D140</f>
+        <v>500401</v>
+      </c>
+      <c r="B140" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D140" s="2">
+        <v>1</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1">
+        <v>100</v>
+      </c>
+      <c r="G140" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="1">
+        <f t="shared" si="7"/>
+        <v>500402</v>
+      </c>
+      <c r="B141" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2">
+        <v>2</v>
+      </c>
+      <c r="E141" s="1">
+        <v>10</v>
+      </c>
+      <c r="F141" s="1">
+        <v>150</v>
+      </c>
+      <c r="G141" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="1">
+        <f t="shared" si="7"/>
+        <v>500403</v>
+      </c>
+      <c r="B142" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2">
+        <v>3</v>
+      </c>
+      <c r="E142" s="1">
+        <v>15</v>
+      </c>
+      <c r="F142" s="1">
+        <v>200</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="1">
+        <f t="shared" si="7"/>
+        <v>500404</v>
+      </c>
+      <c r="B143" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2">
+        <v>4</v>
+      </c>
+      <c r="E143" s="1">
+        <v>20</v>
+      </c>
+      <c r="F143" s="1">
+        <v>250</v>
+      </c>
+      <c r="G143" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="1">
+        <f t="shared" si="7"/>
+        <v>500405</v>
+      </c>
+      <c r="B144" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2">
+        <v>5</v>
+      </c>
+      <c r="E144" s="1">
+        <v>25</v>
+      </c>
+      <c r="F144" s="1">
+        <v>300</v>
+      </c>
+      <c r="G144" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="1">
+        <f t="shared" si="7"/>
+        <v>500501</v>
+      </c>
+      <c r="B145" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1</v>
+      </c>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="1">
+        <v>100</v>
+      </c>
+      <c r="G145" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="1">
+        <f t="shared" si="7"/>
+        <v>500502</v>
+      </c>
+      <c r="B146" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2">
+        <v>2</v>
+      </c>
+      <c r="E146" s="1">
+        <v>10</v>
+      </c>
+      <c r="F146" s="1">
+        <v>150</v>
+      </c>
+      <c r="G146" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="1">
+        <f t="shared" si="7"/>
+        <v>500503</v>
+      </c>
+      <c r="B147" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2">
+        <v>3</v>
+      </c>
+      <c r="E147" s="1">
+        <v>15</v>
+      </c>
+      <c r="F147" s="1">
+        <v>200</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="1">
+        <f t="shared" si="7"/>
+        <v>500504</v>
+      </c>
+      <c r="B148" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2">
+        <v>4</v>
+      </c>
+      <c r="E148" s="1">
+        <v>20</v>
+      </c>
+      <c r="F148" s="1">
+        <v>250</v>
+      </c>
+      <c r="G148" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="1">
+        <f t="shared" si="7"/>
+        <v>500505</v>
+      </c>
+      <c r="B149" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2">
+        <v>5</v>
+      </c>
+      <c r="E149" s="1">
+        <v>25</v>
+      </c>
+      <c r="F149" s="1">
+        <v>300</v>
+      </c>
+      <c r="G149" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="1">
+        <f t="shared" si="7"/>
+        <v>500601</v>
+      </c>
+      <c r="B150" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" s="2">
+        <v>1</v>
+      </c>
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1">
+        <v>100</v>
+      </c>
+      <c r="G150" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="1">
+        <f t="shared" si="7"/>
+        <v>500602</v>
+      </c>
+      <c r="B151" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2">
+        <v>2</v>
+      </c>
+      <c r="E151" s="1">
+        <v>10</v>
+      </c>
+      <c r="F151" s="1">
+        <v>150</v>
+      </c>
+      <c r="G151" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="1">
+        <f t="shared" si="7"/>
+        <v>500603</v>
+      </c>
+      <c r="B152" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2">
+        <v>3</v>
+      </c>
+      <c r="E152" s="1">
+        <v>15</v>
+      </c>
+      <c r="F152" s="1">
+        <v>200</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="1">
+        <f t="shared" si="7"/>
+        <v>500604</v>
+      </c>
+      <c r="B153" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2">
+        <v>4</v>
+      </c>
+      <c r="E153" s="1">
+        <v>20</v>
+      </c>
+      <c r="F153" s="1">
+        <v>250</v>
+      </c>
+      <c r="G153" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="1">
+        <f t="shared" si="7"/>
+        <v>500605</v>
+      </c>
+      <c r="B154" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2">
+        <v>5</v>
+      </c>
+      <c r="E154" s="1">
+        <v>25</v>
+      </c>
+      <c r="F154" s="1">
+        <v>300</v>
+      </c>
+      <c r="G154" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="189" ht="14.25" spans="5:5">
+      <c r="E189" s="6"/>
+    </row>
+    <row r="205" ht="14.25" spans="5:5">
+      <c r="E205" s="6"/>
+    </row>
+    <row r="206" ht="14.25" spans="5:5">
+      <c r="E206" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -155,6 +155,42 @@
     <t>酷盖少年</t>
   </si>
   <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
     <t>文艺青年</t>
   </si>
   <si>
@@ -162,15 +198,6 @@
   </si>
   <si>
     <t>民谣歌手</t>
-  </si>
-  <si>
-    <t>潮流先锋</t>
-  </si>
-  <si>
-    <t>时尚教主</t>
-  </si>
-  <si>
-    <t>街拍达人</t>
   </si>
   <si>
     <t>马拉松客</t>
@@ -182,15 +209,6 @@
     <t>科技极客</t>
   </si>
   <si>
-    <t>运动健将</t>
-  </si>
-  <si>
-    <t>跑酷少年</t>
-  </si>
-  <si>
-    <t>滑板高手</t>
-  </si>
-  <si>
     <t>独立画家</t>
   </si>
   <si>
@@ -200,15 +218,6 @@
     <t>古典乐迷</t>
   </si>
   <si>
-    <t>甜心辣妹</t>
-  </si>
-  <si>
-    <t>活力少女</t>
-  </si>
-  <si>
-    <t>优雅女神</t>
-  </si>
-  <si>
     <t>创业新贵</t>
   </si>
   <si>
@@ -216,15 +225,6 @@
   </si>
   <si>
     <t>氪金大佬</t>
-  </si>
-  <si>
-    <t>健身狂魔</t>
-  </si>
-  <si>
-    <t>单车骑士</t>
-  </si>
-  <si>
-    <t>登山行者</t>
   </si>
   <si>
     <t>穿搭博主</t>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A34" si="1">B20*100+D20</f>
+        <f t="shared" ref="A20:A49" si="1">B20*100+D20</f>
         <v>100401</v>
       </c>
       <c r="B20" s="1">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <f>B35*100+D35</f>
+        <f t="shared" si="1"/>
         <v>200101</v>
       </c>
       <c r="B35" s="1">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <f>B36*100+D36</f>
+        <f t="shared" si="1"/>
         <v>200102</v>
       </c>
       <c r="B36" s="1">
@@ -2047,7 +2047,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <f>B37*100+D37</f>
+        <f t="shared" si="1"/>
         <v>200103</v>
       </c>
       <c r="B37" s="1">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <f>B38*100+D38</f>
+        <f t="shared" si="1"/>
         <v>200104</v>
       </c>
       <c r="B38" s="1">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <f>B39*100+D39</f>
+        <f t="shared" si="1"/>
         <v>200105</v>
       </c>
       <c r="B39" s="1">
@@ -2113,7 +2113,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <f>B40*100+D40</f>
+        <f t="shared" si="1"/>
         <v>200201</v>
       </c>
       <c r="B40" s="1">
@@ -2137,7 +2137,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <f>B41*100+D41</f>
+        <f t="shared" si="1"/>
         <v>200202</v>
       </c>
       <c r="B41" s="1">
@@ -2159,7 +2159,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <f>B42*100+D42</f>
+        <f t="shared" si="1"/>
         <v>200203</v>
       </c>
       <c r="B42" s="1">
@@ -2181,7 +2181,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <f>B43*100+D43</f>
+        <f t="shared" si="1"/>
         <v>200204</v>
       </c>
       <c r="B43" s="1">
@@ -2203,7 +2203,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <f>B44*100+D44</f>
+        <f t="shared" si="1"/>
         <v>200205</v>
       </c>
       <c r="B44" s="1">
@@ -2225,7 +2225,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <f>B45*100+D45</f>
+        <f t="shared" si="1"/>
         <v>200301</v>
       </c>
       <c r="B45" s="1">
@@ -2249,7 +2249,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <f>B46*100+D46</f>
+        <f t="shared" si="1"/>
         <v>200302</v>
       </c>
       <c r="B46" s="1">
@@ -2271,7 +2271,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <f>B47*100+D47</f>
+        <f t="shared" si="1"/>
         <v>200303</v>
       </c>
       <c r="B47" s="1">
@@ -2293,7 +2293,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <f>B48*100+D48</f>
+        <f t="shared" si="1"/>
         <v>200304</v>
       </c>
       <c r="B48" s="1">
@@ -2315,7 +2315,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <f>B49*100+D49</f>
+        <f t="shared" si="1"/>
         <v>200305</v>
       </c>
       <c r="B49" s="1">
@@ -3009,7 +3009,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1">
-        <f t="shared" ref="A80:A94" si="4">B80*100+D80</f>
+        <f t="shared" ref="A80:A109" si="4">B80*100+D80</f>
         <v>300401</v>
       </c>
       <c r="B80" s="1">
@@ -3345,7 +3345,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1">
-        <f>B95*100+D95</f>
+        <f t="shared" si="4"/>
         <v>400101</v>
       </c>
       <c r="B95" s="1">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
-        <f>B96*100+D96</f>
+        <f t="shared" si="4"/>
         <v>400102</v>
       </c>
       <c r="B96" s="1">
@@ -3391,7 +3391,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">
-        <f>B97*100+D97</f>
+        <f t="shared" si="4"/>
         <v>400103</v>
       </c>
       <c r="B97" s="1">
@@ -3413,7 +3413,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1">
-        <f>B98*100+D98</f>
+        <f t="shared" si="4"/>
         <v>400104</v>
       </c>
       <c r="B98" s="1">
@@ -3435,7 +3435,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1">
-        <f>B99*100+D99</f>
+        <f t="shared" si="4"/>
         <v>400105</v>
       </c>
       <c r="B99" s="1">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1">
-        <f>B100*100+D100</f>
+        <f t="shared" si="4"/>
         <v>400201</v>
       </c>
       <c r="B100" s="1">
@@ -3481,7 +3481,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
-        <f>B101*100+D101</f>
+        <f t="shared" si="4"/>
         <v>400202</v>
       </c>
       <c r="B101" s="1">
@@ -3503,7 +3503,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1">
-        <f>B102*100+D102</f>
+        <f t="shared" si="4"/>
         <v>400203</v>
       </c>
       <c r="B102" s="1">
@@ -3525,7 +3525,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1">
-        <f>B103*100+D103</f>
+        <f t="shared" si="4"/>
         <v>400204</v>
       </c>
       <c r="B103" s="1">
@@ -3547,7 +3547,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1">
-        <f>B104*100+D104</f>
+        <f t="shared" si="4"/>
         <v>400205</v>
       </c>
       <c r="B104" s="1">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1">
-        <f>B105*100+D105</f>
+        <f t="shared" si="4"/>
         <v>400301</v>
       </c>
       <c r="B105" s="1">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1">
-        <f>B106*100+D106</f>
+        <f t="shared" si="4"/>
         <v>400302</v>
       </c>
       <c r="B106" s="1">
@@ -3615,7 +3615,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1">
-        <f>B107*100+D107</f>
+        <f t="shared" si="4"/>
         <v>400303</v>
       </c>
       <c r="B107" s="1">
@@ -3637,7 +3637,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1">
-        <f>B108*100+D108</f>
+        <f t="shared" si="4"/>
         <v>400304</v>
       </c>
       <c r="B108" s="1">
@@ -3659,7 +3659,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1">
-        <f>B109*100+D109</f>
+        <f t="shared" si="4"/>
         <v>400305</v>
       </c>
       <c r="B109" s="1">

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -1342,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
@@ -1364,7 +1364,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1">
         <v>150</v>
@@ -1386,7 +1386,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F7" s="1">
         <v>200</v>
@@ -1408,7 +1408,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F8" s="1">
         <v>250</v>
@@ -1430,7 +1430,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F9" s="1">
         <v>300</v>
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>
@@ -1476,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1">
         <v>150</v>
@@ -1498,7 +1498,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F12" s="1">
         <v>200</v>
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F13" s="1">
         <v>250</v>
@@ -1542,7 +1542,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F14" s="1">
         <v>300</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
@@ -1588,7 +1588,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1">
         <v>150</v>
@@ -1610,7 +1610,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F17" s="1">
         <v>200</v>
@@ -1632,7 +1632,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F18" s="1">
         <v>250</v>
@@ -1654,7 +1654,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F19" s="1">
         <v>300</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
@@ -1700,7 +1700,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1">
         <v>150</v>
@@ -1722,7 +1722,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F22" s="1">
         <v>200</v>
@@ -1744,7 +1744,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F23" s="1">
         <v>250</v>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F24" s="1">
         <v>300</v>
@@ -1790,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -1812,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1">
         <v>150</v>
@@ -1834,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F27" s="1">
         <v>200</v>
@@ -1856,7 +1856,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F28" s="1">
         <v>250</v>
@@ -1878,7 +1878,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F29" s="1">
         <v>300</v>
@@ -1902,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1">
         <v>100</v>
@@ -1924,7 +1924,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F31" s="1">
         <v>150</v>
@@ -1946,7 +1946,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F32" s="1">
         <v>200</v>
@@ -1968,7 +1968,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F33" s="1">
         <v>250</v>
@@ -1990,7 +1990,7 @@
         <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F34" s="1">
         <v>300</v>
@@ -2014,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1">
         <v>100</v>
@@ -2036,7 +2036,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1">
         <v>150</v>
@@ -2058,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F37" s="1">
         <v>200</v>
@@ -2080,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F38" s="1">
         <v>250</v>
@@ -2102,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F39" s="1">
         <v>300</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1">
         <v>100</v>
@@ -2148,7 +2148,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F41" s="1">
         <v>150</v>
@@ -2170,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F42" s="1">
         <v>200</v>
@@ -2192,7 +2192,7 @@
         <v>4</v>
       </c>
       <c r="E43" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F43" s="1">
         <v>250</v>
@@ -2214,7 +2214,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F44" s="1">
         <v>300</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1">
         <v>100</v>
@@ -2260,7 +2260,7 @@
         <v>2</v>
       </c>
       <c r="E46" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F46" s="1">
         <v>150</v>
@@ -2282,7 +2282,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F47" s="1">
         <v>200</v>
@@ -2304,7 +2304,7 @@
         <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F48" s="1">
         <v>250</v>
@@ -2326,7 +2326,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F49" s="1">
         <v>300</v>
@@ -2350,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1">
         <v>100</v>
@@ -2372,7 +2372,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1">
         <v>150</v>
@@ -2394,7 +2394,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F52" s="1">
         <v>200</v>
@@ -2416,7 +2416,7 @@
         <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F53" s="1">
         <v>250</v>
@@ -2438,7 +2438,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F54" s="1">
         <v>300</v>
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F55" s="1">
         <v>100</v>
@@ -2484,7 +2484,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1">
         <v>150</v>
@@ -2506,7 +2506,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F57" s="1">
         <v>200</v>
@@ -2528,7 +2528,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F58" s="1">
         <v>250</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="E59" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F59" s="1">
         <v>300</v>
@@ -2574,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1">
         <v>100</v>
@@ -2596,7 +2596,7 @@
         <v>2</v>
       </c>
       <c r="E61" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1">
         <v>150</v>
@@ -2618,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="E62" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F62" s="1">
         <v>200</v>
@@ -2640,7 +2640,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F63" s="1">
         <v>250</v>
@@ -2662,7 +2662,7 @@
         <v>5</v>
       </c>
       <c r="E64" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F64" s="1">
         <v>300</v>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F65" s="1">
         <v>100</v>
@@ -2708,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F66" s="1">
         <v>150</v>
@@ -2730,7 +2730,7 @@
         <v>3</v>
       </c>
       <c r="E67" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F67" s="1">
         <v>200</v>
@@ -2752,7 +2752,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F68" s="1">
         <v>250</v>
@@ -2774,7 +2774,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F69" s="1">
         <v>300</v>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F70" s="1">
         <v>100</v>
@@ -2820,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="E71" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F71" s="1">
         <v>150</v>
@@ -2842,7 +2842,7 @@
         <v>3</v>
       </c>
       <c r="E72" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F72" s="1">
         <v>200</v>
@@ -2864,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F73" s="1">
         <v>250</v>
@@ -2886,7 +2886,7 @@
         <v>5</v>
       </c>
       <c r="E74" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F74" s="1">
         <v>300</v>
@@ -2910,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F75" s="1">
         <v>100</v>
@@ -2932,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F76" s="1">
         <v>150</v>
@@ -2954,7 +2954,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F77" s="1">
         <v>200</v>
@@ -2976,7 +2976,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F78" s="1">
         <v>250</v>
@@ -2998,7 +2998,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F79" s="1">
         <v>300</v>
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1">
         <v>100</v>
@@ -3044,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="E81" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F81" s="1">
         <v>150</v>
@@ -3066,7 +3066,7 @@
         <v>3</v>
       </c>
       <c r="E82" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F82" s="1">
         <v>200</v>
@@ -3088,7 +3088,7 @@
         <v>4</v>
       </c>
       <c r="E83" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F83" s="1">
         <v>250</v>
@@ -3110,7 +3110,7 @@
         <v>5</v>
       </c>
       <c r="E84" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F84" s="1">
         <v>300</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1">
         <v>100</v>
@@ -3156,7 +3156,7 @@
         <v>2</v>
       </c>
       <c r="E86" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F86" s="1">
         <v>150</v>
@@ -3178,7 +3178,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F87" s="1">
         <v>200</v>
@@ -3200,7 +3200,7 @@
         <v>4</v>
       </c>
       <c r="E88" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F88" s="1">
         <v>250</v>
@@ -3222,7 +3222,7 @@
         <v>5</v>
       </c>
       <c r="E89" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F89" s="1">
         <v>300</v>
@@ -3246,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F90" s="1">
         <v>100</v>
@@ -3268,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F91" s="1">
         <v>150</v>
@@ -3290,7 +3290,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F92" s="1">
         <v>200</v>
@@ -3312,7 +3312,7 @@
         <v>4</v>
       </c>
       <c r="E93" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F93" s="1">
         <v>250</v>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="E94" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F94" s="1">
         <v>300</v>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1">
         <v>100</v>
@@ -3380,7 +3380,7 @@
         <v>2</v>
       </c>
       <c r="E96" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F96" s="1">
         <v>150</v>
@@ -3402,7 +3402,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F97" s="1">
         <v>200</v>
@@ -3424,7 +3424,7 @@
         <v>4</v>
       </c>
       <c r="E98" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F98" s="1">
         <v>250</v>
@@ -3446,7 +3446,7 @@
         <v>5</v>
       </c>
       <c r="E99" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F99" s="1">
         <v>300</v>
@@ -3470,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F100" s="1">
         <v>100</v>
@@ -3492,7 +3492,7 @@
         <v>2</v>
       </c>
       <c r="E101" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F101" s="1">
         <v>150</v>
@@ -3514,7 +3514,7 @@
         <v>3</v>
       </c>
       <c r="E102" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F102" s="1">
         <v>200</v>
@@ -3536,7 +3536,7 @@
         <v>4</v>
       </c>
       <c r="E103" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F103" s="1">
         <v>250</v>
@@ -3558,7 +3558,7 @@
         <v>5</v>
       </c>
       <c r="E104" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F104" s="1">
         <v>300</v>
@@ -3582,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1">
         <v>100</v>
@@ -3604,7 +3604,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F106" s="1">
         <v>150</v>
@@ -3626,7 +3626,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F107" s="1">
         <v>200</v>
@@ -3648,7 +3648,7 @@
         <v>4</v>
       </c>
       <c r="E108" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F108" s="1">
         <v>250</v>
@@ -3670,7 +3670,7 @@
         <v>5</v>
       </c>
       <c r="E109" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F109" s="1">
         <v>300</v>
@@ -3694,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="E110" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1">
         <v>100</v>
@@ -3716,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F111" s="1">
         <v>150</v>
@@ -3738,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F112" s="1">
         <v>200</v>
@@ -3760,7 +3760,7 @@
         <v>4</v>
       </c>
       <c r="E113" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F113" s="1">
         <v>250</v>
@@ -3782,7 +3782,7 @@
         <v>5</v>
       </c>
       <c r="E114" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F114" s="1">
         <v>300</v>
@@ -3806,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1">
         <v>100</v>
@@ -3828,7 +3828,7 @@
         <v>2</v>
       </c>
       <c r="E116" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F116" s="1">
         <v>150</v>
@@ -3850,7 +3850,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F117" s="1">
         <v>200</v>
@@ -3872,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="E118" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F118" s="1">
         <v>250</v>
@@ -3894,7 +3894,7 @@
         <v>5</v>
       </c>
       <c r="E119" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F119" s="1">
         <v>300</v>
@@ -3918,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="E120" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1">
         <v>100</v>
@@ -3940,7 +3940,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F121" s="1">
         <v>150</v>
@@ -3962,7 +3962,7 @@
         <v>3</v>
       </c>
       <c r="E122" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F122" s="1">
         <v>200</v>
@@ -3984,7 +3984,7 @@
         <v>4</v>
       </c>
       <c r="E123" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F123" s="1">
         <v>250</v>
@@ -4006,7 +4006,7 @@
         <v>5</v>
       </c>
       <c r="E124" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F124" s="1">
         <v>300</v>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="E125" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F126" s="1">
         <v>150</v>
@@ -4074,7 +4074,7 @@
         <v>3</v>
       </c>
       <c r="E127" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F127" s="1">
         <v>200</v>
@@ -4096,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="E128" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F128" s="1">
         <v>250</v>
@@ -4118,7 +4118,7 @@
         <v>5</v>
       </c>
       <c r="E129" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F129" s="1">
         <v>300</v>
@@ -4142,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="E130" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F130" s="1">
         <v>100</v>
@@ -4164,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F131" s="1">
         <v>150</v>
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="E132" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F132" s="1">
         <v>200</v>
@@ -4208,7 +4208,7 @@
         <v>4</v>
       </c>
       <c r="E133" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F133" s="1">
         <v>250</v>
@@ -4230,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="E134" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F134" s="1">
         <v>300</v>
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="E135" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F135" s="1">
         <v>100</v>
@@ -4276,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F136" s="1">
         <v>150</v>
@@ -4298,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="E137" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F137" s="1">
         <v>200</v>
@@ -4320,7 +4320,7 @@
         <v>4</v>
       </c>
       <c r="E138" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F138" s="1">
         <v>250</v>
@@ -4342,7 +4342,7 @@
         <v>5</v>
       </c>
       <c r="E139" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F139" s="1">
         <v>300</v>
@@ -4366,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="E140" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F140" s="1">
         <v>100</v>
@@ -4388,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="E141" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F141" s="1">
         <v>150</v>
@@ -4410,7 +4410,7 @@
         <v>3</v>
       </c>
       <c r="E142" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F142" s="1">
         <v>200</v>
@@ -4432,7 +4432,7 @@
         <v>4</v>
       </c>
       <c r="E143" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F143" s="1">
         <v>250</v>
@@ -4454,7 +4454,7 @@
         <v>5</v>
       </c>
       <c r="E144" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F144" s="1">
         <v>300</v>
@@ -4478,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="E145" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F145" s="1">
         <v>100</v>
@@ -4500,7 +4500,7 @@
         <v>2</v>
       </c>
       <c r="E146" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F146" s="1">
         <v>150</v>
@@ -4522,7 +4522,7 @@
         <v>3</v>
       </c>
       <c r="E147" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F147" s="1">
         <v>200</v>
@@ -4544,7 +4544,7 @@
         <v>4</v>
       </c>
       <c r="E148" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F148" s="1">
         <v>250</v>
@@ -4566,7 +4566,7 @@
         <v>5</v>
       </c>
       <c r="E149" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F149" s="1">
         <v>300</v>
@@ -4590,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="E150" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F150" s="1">
         <v>100</v>
@@ -4612,7 +4612,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F151" s="1">
         <v>150</v>
@@ -4634,7 +4634,7 @@
         <v>3</v>
       </c>
       <c r="E152" s="1">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="F152" s="1">
         <v>200</v>
@@ -4656,7 +4656,7 @@
         <v>4</v>
       </c>
       <c r="E153" s="1">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="F153" s="1">
         <v>250</v>
@@ -4678,7 +4678,7 @@
         <v>5</v>
       </c>
       <c r="E154" s="1">
-        <v>25</v>
+        <v>999999</v>
       </c>
       <c r="F154" s="1">
         <v>300</v>

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -85,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -234,6 +239,21 @@
   </si>
   <si>
     <t>高定女王</t>
+  </si>
+  <si>
+    <t>独立女士</t>
+  </si>
+  <si>
+    <t>夜色女神</t>
+  </si>
+  <si>
+    <t>优雅名媛</t>
+  </si>
+  <si>
+    <t>时尚先锋</t>
+  </si>
+  <si>
+    <t>商务精英</t>
   </si>
 </sst>
 </file>
@@ -904,7 +924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -922,6 +942,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -4687,14 +4710,114 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="1">
+        <f>B155*100+D155</f>
+        <v>900101</v>
+      </c>
+      <c r="B155" s="6">
+        <v>9001</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D155" s="6">
+        <v>1</v>
+      </c>
+      <c r="E155" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F155" s="6"/>
+      <c r="G155" s="6"/>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="1">
+        <f>B156*100+D156</f>
+        <v>900201</v>
+      </c>
+      <c r="B156" s="6">
+        <v>9002</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D156" s="6">
+        <v>1</v>
+      </c>
+      <c r="E156" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="1">
+        <f>B157*100+D157</f>
+        <v>900301</v>
+      </c>
+      <c r="B157" s="6">
+        <v>9003</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D157" s="6">
+        <v>1</v>
+      </c>
+      <c r="E157" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F157" s="6"/>
+      <c r="G157" s="6"/>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="1">
+        <f>B158*100+D158</f>
+        <v>900401</v>
+      </c>
+      <c r="B158" s="6">
+        <v>9004</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D158" s="6">
+        <v>1</v>
+      </c>
+      <c r="E158" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="1">
+        <f>B159*100+D159</f>
+        <v>900501</v>
+      </c>
+      <c r="B159" s="6">
+        <v>9005</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D159" s="6">
+        <v>1</v>
+      </c>
+      <c r="E159" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F159" s="6"/>
+      <c r="G159" s="6"/>
+    </row>
     <row r="189" ht="14.25" spans="5:5">
-      <c r="E189" s="6"/>
+      <c r="E189" s="7"/>
     </row>
     <row r="205" ht="14.25" spans="5:5">
-      <c r="E205" s="6"/>
+      <c r="E205" s="7"/>
     </row>
     <row r="206" ht="14.25" spans="5:5">
-      <c r="E206" s="6"/>
+      <c r="E206" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="VisitorStar" sheetId="8" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -90,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -254,6 +255,21 @@
   </si>
   <si>
     <t>商务精英</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>金</t>
   </si>
 </sst>
 </file>
@@ -924,7 +940,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -942,9 +958,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1368,7 +1381,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1">
         <v>2000</v>
@@ -1390,10 +1403,10 @@
         <v>60</v>
       </c>
       <c r="F6" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G6" s="1">
-        <v>3000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1412,10 +1425,10 @@
         <v>180</v>
       </c>
       <c r="F7" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1">
-        <v>4000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1434,10 +1447,10 @@
         <v>540</v>
       </c>
       <c r="F8" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G8" s="1">
-        <v>5000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1456,10 +1469,10 @@
         <v>999999</v>
       </c>
       <c r="F9" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1">
-        <v>6000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1480,9 +1493,10 @@
         <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
+        <f>G5</f>
         <v>2000</v>
       </c>
     </row>
@@ -1502,10 +1516,11 @@
         <v>60</v>
       </c>
       <c r="F11" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G11" s="1">
-        <v>3000</v>
+        <f>G6</f>
+        <v>2600</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1524,10 +1539,11 @@
         <v>180</v>
       </c>
       <c r="F12" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1">
-        <v>4000</v>
+        <f>G7</f>
+        <v>3200</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1546,10 +1562,11 @@
         <v>540</v>
       </c>
       <c r="F13" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G13" s="1">
-        <v>5000</v>
+        <f>G8</f>
+        <v>3800</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1568,10 +1585,11 @@
         <v>999999</v>
       </c>
       <c r="F14" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G14" s="1">
-        <v>6000</v>
+        <f>G9</f>
+        <v>4400</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1592,9 +1610,10 @@
         <v>20</v>
       </c>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1">
+        <f t="shared" ref="G15:G34" si="1">G10</f>
         <v>2000</v>
       </c>
     </row>
@@ -1614,10 +1633,11 @@
         <v>60</v>
       </c>
       <c r="F16" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G16" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1636,10 +1656,11 @@
         <v>180</v>
       </c>
       <c r="F17" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1">
-        <v>4000</v>
+        <f t="shared" si="1"/>
+        <v>3200</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1658,10 +1679,11 @@
         <v>540</v>
       </c>
       <c r="F18" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G18" s="1">
-        <v>5000</v>
+        <f t="shared" si="1"/>
+        <v>3800</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1680,15 +1702,16 @@
         <v>999999</v>
       </c>
       <c r="F19" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G19" s="1">
-        <v>6000</v>
+        <f t="shared" si="1"/>
+        <v>4400</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A49" si="1">B20*100+D20</f>
+        <f t="shared" ref="A20:A49" si="2">B20*100+D20</f>
         <v>100401</v>
       </c>
       <c r="B20" s="1">
@@ -1704,15 +1727,16 @@
         <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G20" s="1">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100402</v>
       </c>
       <c r="B21" s="1">
@@ -1726,15 +1750,16 @@
         <v>60</v>
       </c>
       <c r="F21" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G21" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100403</v>
       </c>
       <c r="B22" s="1">
@@ -1748,15 +1773,16 @@
         <v>180</v>
       </c>
       <c r="F22" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G22" s="1">
-        <v>4000</v>
+        <f t="shared" si="1"/>
+        <v>3200</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100404</v>
       </c>
       <c r="B23" s="1">
@@ -1770,15 +1796,16 @@
         <v>540</v>
       </c>
       <c r="F23" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G23" s="1">
-        <v>5000</v>
+        <f t="shared" si="1"/>
+        <v>3800</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100405</v>
       </c>
       <c r="B24" s="1">
@@ -1792,15 +1819,16 @@
         <v>999999</v>
       </c>
       <c r="F24" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G24" s="1">
-        <v>6000</v>
+        <f t="shared" si="1"/>
+        <v>4400</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100501</v>
       </c>
       <c r="B25" s="1">
@@ -1816,15 +1844,16 @@
         <v>20</v>
       </c>
       <c r="F25" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G25" s="1">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100502</v>
       </c>
       <c r="B26" s="1">
@@ -1838,15 +1867,16 @@
         <v>60</v>
       </c>
       <c r="F26" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G26" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100503</v>
       </c>
       <c r="B27" s="1">
@@ -1860,15 +1890,16 @@
         <v>180</v>
       </c>
       <c r="F27" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G27" s="1">
-        <v>4000</v>
+        <f t="shared" si="1"/>
+        <v>3200</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100504</v>
       </c>
       <c r="B28" s="1">
@@ -1882,15 +1913,16 @@
         <v>540</v>
       </c>
       <c r="F28" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G28" s="1">
-        <v>5000</v>
+        <f t="shared" si="1"/>
+        <v>3800</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100505</v>
       </c>
       <c r="B29" s="1">
@@ -1904,15 +1936,16 @@
         <v>999999</v>
       </c>
       <c r="F29" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G29" s="1">
-        <v>6000</v>
+        <f t="shared" si="1"/>
+        <v>4400</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100601</v>
       </c>
       <c r="B30" s="1">
@@ -1928,15 +1961,16 @@
         <v>20</v>
       </c>
       <c r="F30" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G30" s="1">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100602</v>
       </c>
       <c r="B31" s="1">
@@ -1950,15 +1984,16 @@
         <v>60</v>
       </c>
       <c r="F31" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G31" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100603</v>
       </c>
       <c r="B32" s="1">
@@ -1972,15 +2007,16 @@
         <v>180</v>
       </c>
       <c r="F32" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G32" s="1">
-        <v>4000</v>
+        <f t="shared" si="1"/>
+        <v>3200</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100604</v>
       </c>
       <c r="B33" s="1">
@@ -1994,15 +2030,16 @@
         <v>540</v>
       </c>
       <c r="F33" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G33" s="1">
-        <v>5000</v>
+        <f t="shared" si="1"/>
+        <v>3800</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100605</v>
       </c>
       <c r="B34" s="1">
@@ -2016,15 +2053,16 @@
         <v>999999</v>
       </c>
       <c r="F34" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G34" s="1">
-        <v>6000</v>
+        <f t="shared" si="1"/>
+        <v>4400</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200101</v>
       </c>
       <c r="B35" s="1">
@@ -2040,15 +2078,15 @@
         <v>20</v>
       </c>
       <c r="F35" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G35" s="1">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200102</v>
       </c>
       <c r="B36" s="1">
@@ -2062,15 +2100,15 @@
         <v>60</v>
       </c>
       <c r="F36" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G36" s="1">
-        <v>3000</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200103</v>
       </c>
       <c r="B37" s="1">
@@ -2084,15 +2122,15 @@
         <v>180</v>
       </c>
       <c r="F37" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G37" s="1">
-        <v>4000</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200104</v>
       </c>
       <c r="B38" s="1">
@@ -2106,15 +2144,15 @@
         <v>540</v>
       </c>
       <c r="F38" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G38" s="1">
-        <v>5000</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200105</v>
       </c>
       <c r="B39" s="1">
@@ -2128,15 +2166,15 @@
         <v>999999</v>
       </c>
       <c r="F39" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G39" s="1">
-        <v>6000</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200201</v>
       </c>
       <c r="B40" s="1">
@@ -2152,15 +2190,16 @@
         <v>20</v>
       </c>
       <c r="F40" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G40" s="1">
-        <v>2000</v>
+        <f>G35</f>
+        <v>2500</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200202</v>
       </c>
       <c r="B41" s="1">
@@ -2174,15 +2213,16 @@
         <v>60</v>
       </c>
       <c r="F41" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G41" s="1">
-        <v>3000</v>
+        <f t="shared" ref="G41:G64" si="3">G36</f>
+        <v>3100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200203</v>
       </c>
       <c r="B42" s="1">
@@ -2196,15 +2236,16 @@
         <v>180</v>
       </c>
       <c r="F42" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G42" s="1">
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3700</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200204</v>
       </c>
       <c r="B43" s="1">
@@ -2218,15 +2259,16 @@
         <v>540</v>
       </c>
       <c r="F43" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G43" s="1">
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>4300</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200205</v>
       </c>
       <c r="B44" s="1">
@@ -2240,15 +2282,16 @@
         <v>999999</v>
       </c>
       <c r="F44" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G44" s="1">
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>4900</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200301</v>
       </c>
       <c r="B45" s="1">
@@ -2264,15 +2307,16 @@
         <v>20</v>
       </c>
       <c r="F45" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G45" s="1">
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200302</v>
       </c>
       <c r="B46" s="1">
@@ -2286,15 +2330,16 @@
         <v>60</v>
       </c>
       <c r="F46" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G46" s="1">
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>3100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200303</v>
       </c>
       <c r="B47" s="1">
@@ -2308,15 +2353,16 @@
         <v>180</v>
       </c>
       <c r="F47" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G47" s="1">
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3700</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200304</v>
       </c>
       <c r="B48" s="1">
@@ -2330,15 +2376,16 @@
         <v>540</v>
       </c>
       <c r="F48" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G48" s="1">
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>4300</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200305</v>
       </c>
       <c r="B49" s="1">
@@ -2352,15 +2399,16 @@
         <v>999999</v>
       </c>
       <c r="F49" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G49" s="1">
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>4900</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <f t="shared" ref="A50:A64" si="2">B50*100+D50</f>
+        <f t="shared" ref="A50:A64" si="4">B50*100+D50</f>
         <v>200401</v>
       </c>
       <c r="B50" s="1">
@@ -2376,15 +2424,16 @@
         <v>20</v>
       </c>
       <c r="F50" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G50" s="1">
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200402</v>
       </c>
       <c r="B51" s="1">
@@ -2398,15 +2447,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G51" s="1">
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>3100</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200403</v>
       </c>
       <c r="B52" s="1">
@@ -2420,15 +2470,16 @@
         <v>180</v>
       </c>
       <c r="F52" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G52" s="1">
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3700</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200404</v>
       </c>
       <c r="B53" s="1">
@@ -2442,15 +2493,16 @@
         <v>540</v>
       </c>
       <c r="F53" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G53" s="1">
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>4300</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200405</v>
       </c>
       <c r="B54" s="1">
@@ -2464,15 +2516,16 @@
         <v>999999</v>
       </c>
       <c r="F54" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G54" s="1">
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>4900</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200501</v>
       </c>
       <c r="B55" s="1">
@@ -2488,15 +2541,16 @@
         <v>20</v>
       </c>
       <c r="F55" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G55" s="1">
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200502</v>
       </c>
       <c r="B56" s="1">
@@ -2510,15 +2564,16 @@
         <v>60</v>
       </c>
       <c r="F56" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G56" s="1">
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>3100</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200503</v>
       </c>
       <c r="B57" s="1">
@@ -2532,15 +2587,16 @@
         <v>180</v>
       </c>
       <c r="F57" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G57" s="1">
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3700</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200504</v>
       </c>
       <c r="B58" s="1">
@@ -2554,15 +2610,16 @@
         <v>540</v>
       </c>
       <c r="F58" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G58" s="1">
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>4300</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200505</v>
       </c>
       <c r="B59" s="1">
@@ -2576,15 +2633,16 @@
         <v>999999</v>
       </c>
       <c r="F59" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G59" s="1">
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>4900</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200601</v>
       </c>
       <c r="B60" s="1">
@@ -2600,15 +2658,16 @@
         <v>20</v>
       </c>
       <c r="F60" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G60" s="1">
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200602</v>
       </c>
       <c r="B61" s="1">
@@ -2622,15 +2681,16 @@
         <v>60</v>
       </c>
       <c r="F61" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G61" s="1">
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>3100</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200603</v>
       </c>
       <c r="B62" s="1">
@@ -2644,15 +2704,16 @@
         <v>180</v>
       </c>
       <c r="F62" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G62" s="1">
-        <v>4000</v>
+        <f t="shared" si="3"/>
+        <v>3700</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200604</v>
       </c>
       <c r="B63" s="1">
@@ -2666,15 +2727,16 @@
         <v>540</v>
       </c>
       <c r="F63" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G63" s="1">
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>4300</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200605</v>
       </c>
       <c r="B64" s="1">
@@ -2688,15 +2750,16 @@
         <v>999999</v>
       </c>
       <c r="F64" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G64" s="1">
-        <v>6000</v>
+        <f t="shared" si="3"/>
+        <v>4900</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <f t="shared" ref="A65:A81" si="3">B65*100+D65</f>
+        <f t="shared" ref="A65:A81" si="5">B65*100+D65</f>
         <v>300101</v>
       </c>
       <c r="B65" s="1">
@@ -2712,15 +2775,15 @@
         <v>20</v>
       </c>
       <c r="F65" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G65" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300102</v>
       </c>
       <c r="B66" s="1">
@@ -2734,15 +2797,15 @@
         <v>60</v>
       </c>
       <c r="F66" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G66" s="1">
-        <v>3000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300103</v>
       </c>
       <c r="B67" s="1">
@@ -2756,15 +2819,15 @@
         <v>180</v>
       </c>
       <c r="F67" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G67" s="1">
-        <v>4000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300104</v>
       </c>
       <c r="B68" s="1">
@@ -2778,15 +2841,15 @@
         <v>540</v>
       </c>
       <c r="F68" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G68" s="1">
-        <v>5000</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300105</v>
       </c>
       <c r="B69" s="1">
@@ -2800,15 +2863,15 @@
         <v>999999</v>
       </c>
       <c r="F69" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G69" s="1">
-        <v>6000</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300201</v>
       </c>
       <c r="B70" s="1">
@@ -2824,15 +2887,16 @@
         <v>20</v>
       </c>
       <c r="F70" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G70" s="1">
-        <v>2000</v>
+        <f>G65</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300202</v>
       </c>
       <c r="B71" s="1">
@@ -2846,15 +2910,16 @@
         <v>60</v>
       </c>
       <c r="F71" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G71" s="1">
-        <v>3000</v>
+        <f t="shared" ref="G71:G94" si="6">G66</f>
+        <v>3600</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300203</v>
       </c>
       <c r="B72" s="1">
@@ -2868,15 +2933,16 @@
         <v>180</v>
       </c>
       <c r="F72" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G72" s="1">
-        <v>4000</v>
+        <f t="shared" si="6"/>
+        <v>4200</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300204</v>
       </c>
       <c r="B73" s="1">
@@ -2890,15 +2956,16 @@
         <v>540</v>
       </c>
       <c r="F73" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G73" s="1">
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4800</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300205</v>
       </c>
       <c r="B74" s="1">
@@ -2912,15 +2979,16 @@
         <v>999999</v>
       </c>
       <c r="F74" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G74" s="1">
-        <v>6000</v>
+        <f t="shared" si="6"/>
+        <v>5400</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300301</v>
       </c>
       <c r="B75" s="1">
@@ -2936,15 +3004,16 @@
         <v>20</v>
       </c>
       <c r="F75" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G75" s="1">
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300302</v>
       </c>
       <c r="B76" s="1">
@@ -2958,15 +3027,16 @@
         <v>60</v>
       </c>
       <c r="F76" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G76" s="1">
-        <v>3000</v>
+        <f t="shared" si="6"/>
+        <v>3600</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300303</v>
       </c>
       <c r="B77" s="1">
@@ -2980,15 +3050,16 @@
         <v>180</v>
       </c>
       <c r="F77" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G77" s="1">
-        <v>4000</v>
+        <f t="shared" si="6"/>
+        <v>4200</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300304</v>
       </c>
       <c r="B78" s="1">
@@ -3002,15 +3073,16 @@
         <v>540</v>
       </c>
       <c r="F78" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G78" s="1">
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4800</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300305</v>
       </c>
       <c r="B79" s="1">
@@ -3024,15 +3096,16 @@
         <v>999999</v>
       </c>
       <c r="F79" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G79" s="1">
-        <v>6000</v>
+        <f t="shared" si="6"/>
+        <v>5400</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1">
-        <f t="shared" ref="A80:A109" si="4">B80*100+D80</f>
+        <f t="shared" ref="A80:A109" si="7">B80*100+D80</f>
         <v>300401</v>
       </c>
       <c r="B80" s="1">
@@ -3048,15 +3121,16 @@
         <v>20</v>
       </c>
       <c r="F80" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G80" s="1">
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300402</v>
       </c>
       <c r="B81" s="1">
@@ -3070,15 +3144,16 @@
         <v>60</v>
       </c>
       <c r="F81" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G81" s="1">
-        <v>3000</v>
+        <f t="shared" si="6"/>
+        <v>3600</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300403</v>
       </c>
       <c r="B82" s="1">
@@ -3092,15 +3167,16 @@
         <v>180</v>
       </c>
       <c r="F82" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G82" s="1">
-        <v>4000</v>
+        <f t="shared" si="6"/>
+        <v>4200</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300404</v>
       </c>
       <c r="B83" s="1">
@@ -3114,15 +3190,16 @@
         <v>540</v>
       </c>
       <c r="F83" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G83" s="1">
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4800</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300405</v>
       </c>
       <c r="B84" s="1">
@@ -3136,15 +3213,16 @@
         <v>999999</v>
       </c>
       <c r="F84" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G84" s="1">
-        <v>6000</v>
+        <f t="shared" si="6"/>
+        <v>5400</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300501</v>
       </c>
       <c r="B85" s="1">
@@ -3160,15 +3238,16 @@
         <v>20</v>
       </c>
       <c r="F85" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G85" s="1">
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300502</v>
       </c>
       <c r="B86" s="1">
@@ -3182,15 +3261,16 @@
         <v>60</v>
       </c>
       <c r="F86" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G86" s="1">
-        <v>3000</v>
+        <f t="shared" si="6"/>
+        <v>3600</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300503</v>
       </c>
       <c r="B87" s="1">
@@ -3204,15 +3284,16 @@
         <v>180</v>
       </c>
       <c r="F87" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G87" s="1">
-        <v>4000</v>
+        <f t="shared" si="6"/>
+        <v>4200</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300504</v>
       </c>
       <c r="B88" s="1">
@@ -3226,15 +3307,16 @@
         <v>540</v>
       </c>
       <c r="F88" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G88" s="1">
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4800</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300505</v>
       </c>
       <c r="B89" s="1">
@@ -3248,15 +3330,16 @@
         <v>999999</v>
       </c>
       <c r="F89" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G89" s="1">
-        <v>6000</v>
+        <f t="shared" si="6"/>
+        <v>5400</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300601</v>
       </c>
       <c r="B90" s="1">
@@ -3272,15 +3355,16 @@
         <v>20</v>
       </c>
       <c r="F90" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G90" s="1">
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300602</v>
       </c>
       <c r="B91" s="1">
@@ -3294,15 +3378,16 @@
         <v>60</v>
       </c>
       <c r="F91" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G91" s="1">
-        <v>3000</v>
+        <f t="shared" si="6"/>
+        <v>3600</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300603</v>
       </c>
       <c r="B92" s="1">
@@ -3316,15 +3401,16 @@
         <v>180</v>
       </c>
       <c r="F92" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G92" s="1">
-        <v>4000</v>
+        <f t="shared" si="6"/>
+        <v>4200</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300604</v>
       </c>
       <c r="B93" s="1">
@@ -3338,15 +3424,16 @@
         <v>540</v>
       </c>
       <c r="F93" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G93" s="1">
-        <v>5000</v>
+        <f t="shared" si="6"/>
+        <v>4800</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300605</v>
       </c>
       <c r="B94" s="1">
@@ -3360,15 +3447,16 @@
         <v>999999</v>
       </c>
       <c r="F94" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G94" s="1">
-        <v>6000</v>
+        <f t="shared" si="6"/>
+        <v>5400</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400101</v>
       </c>
       <c r="B95" s="1">
@@ -3384,15 +3472,15 @@
         <v>20</v>
       </c>
       <c r="F95" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G95" s="1">
-        <v>2000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400102</v>
       </c>
       <c r="B96" s="1">
@@ -3406,15 +3494,15 @@
         <v>60</v>
       </c>
       <c r="F96" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G96" s="1">
-        <v>3000</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400103</v>
       </c>
       <c r="B97" s="1">
@@ -3428,15 +3516,15 @@
         <v>180</v>
       </c>
       <c r="F97" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G97" s="1">
-        <v>4000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400104</v>
       </c>
       <c r="B98" s="1">
@@ -3450,15 +3538,15 @@
         <v>540</v>
       </c>
       <c r="F98" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G98" s="1">
-        <v>5000</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400105</v>
       </c>
       <c r="B99" s="1">
@@ -3472,15 +3560,15 @@
         <v>999999</v>
       </c>
       <c r="F99" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G99" s="1">
-        <v>6000</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400201</v>
       </c>
       <c r="B100" s="1">
@@ -3496,15 +3584,16 @@
         <v>20</v>
       </c>
       <c r="F100" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G100" s="1">
-        <v>2000</v>
+        <f>G95</f>
+        <v>3500</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400202</v>
       </c>
       <c r="B101" s="1">
@@ -3518,15 +3607,16 @@
         <v>60</v>
       </c>
       <c r="F101" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G101" s="1">
-        <v>3000</v>
+        <f t="shared" ref="G101:G124" si="8">G96</f>
+        <v>4100</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400203</v>
       </c>
       <c r="B102" s="1">
@@ -3540,15 +3630,16 @@
         <v>180</v>
       </c>
       <c r="F102" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G102" s="1">
-        <v>4000</v>
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400204</v>
       </c>
       <c r="B103" s="1">
@@ -3562,15 +3653,16 @@
         <v>540</v>
       </c>
       <c r="F103" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G103" s="1">
-        <v>5000</v>
+        <f t="shared" si="8"/>
+        <v>5300</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400205</v>
       </c>
       <c r="B104" s="1">
@@ -3584,15 +3676,16 @@
         <v>999999</v>
       </c>
       <c r="F104" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G104" s="1">
-        <v>6000</v>
+        <f t="shared" si="8"/>
+        <v>5900</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400301</v>
       </c>
       <c r="B105" s="1">
@@ -3608,15 +3701,16 @@
         <v>20</v>
       </c>
       <c r="F105" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G105" s="1">
-        <v>2000</v>
+        <f t="shared" si="8"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400302</v>
       </c>
       <c r="B106" s="1">
@@ -3630,15 +3724,16 @@
         <v>60</v>
       </c>
       <c r="F106" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G106" s="1">
-        <v>3000</v>
+        <f t="shared" si="8"/>
+        <v>4100</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400303</v>
       </c>
       <c r="B107" s="1">
@@ -3652,15 +3747,16 @@
         <v>180</v>
       </c>
       <c r="F107" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G107" s="1">
-        <v>4000</v>
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400304</v>
       </c>
       <c r="B108" s="1">
@@ -3674,15 +3770,16 @@
         <v>540</v>
       </c>
       <c r="F108" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G108" s="1">
-        <v>5000</v>
+        <f t="shared" si="8"/>
+        <v>5300</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>400305</v>
       </c>
       <c r="B109" s="1">
@@ -3696,15 +3793,16 @@
         <v>999999</v>
       </c>
       <c r="F109" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G109" s="1">
-        <v>6000</v>
+        <f t="shared" si="8"/>
+        <v>5900</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="1">
-        <f t="shared" ref="A110:A124" si="5">B110*100+D110</f>
+        <f t="shared" ref="A110:A124" si="9">B110*100+D110</f>
         <v>400401</v>
       </c>
       <c r="B110" s="1">
@@ -3720,15 +3818,16 @@
         <v>20</v>
       </c>
       <c r="F110" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G110" s="1">
-        <v>2000</v>
+        <f t="shared" si="8"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400402</v>
       </c>
       <c r="B111" s="1">
@@ -3742,15 +3841,16 @@
         <v>60</v>
       </c>
       <c r="F111" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G111" s="1">
-        <v>3000</v>
+        <f t="shared" si="8"/>
+        <v>4100</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400403</v>
       </c>
       <c r="B112" s="1">
@@ -3764,15 +3864,16 @@
         <v>180</v>
       </c>
       <c r="F112" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G112" s="1">
-        <v>4000</v>
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400404</v>
       </c>
       <c r="B113" s="1">
@@ -3786,15 +3887,16 @@
         <v>540</v>
       </c>
       <c r="F113" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G113" s="1">
-        <v>5000</v>
+        <f t="shared" si="8"/>
+        <v>5300</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400405</v>
       </c>
       <c r="B114" s="1">
@@ -3808,15 +3910,16 @@
         <v>999999</v>
       </c>
       <c r="F114" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G114" s="1">
-        <v>6000</v>
+        <f t="shared" si="8"/>
+        <v>5900</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400501</v>
       </c>
       <c r="B115" s="1">
@@ -3832,15 +3935,16 @@
         <v>20</v>
       </c>
       <c r="F115" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G115" s="1">
-        <v>2000</v>
+        <f t="shared" si="8"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400502</v>
       </c>
       <c r="B116" s="1">
@@ -3854,15 +3958,16 @@
         <v>60</v>
       </c>
       <c r="F116" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G116" s="1">
-        <v>3000</v>
+        <f t="shared" si="8"/>
+        <v>4100</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400503</v>
       </c>
       <c r="B117" s="1">
@@ -3876,15 +3981,16 @@
         <v>180</v>
       </c>
       <c r="F117" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G117" s="1">
-        <v>4000</v>
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400504</v>
       </c>
       <c r="B118" s="1">
@@ -3898,15 +4004,16 @@
         <v>540</v>
       </c>
       <c r="F118" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G118" s="1">
-        <v>5000</v>
+        <f t="shared" si="8"/>
+        <v>5300</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400505</v>
       </c>
       <c r="B119" s="1">
@@ -3920,15 +4027,16 @@
         <v>999999</v>
       </c>
       <c r="F119" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G119" s="1">
-        <v>6000</v>
+        <f t="shared" si="8"/>
+        <v>5900</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400601</v>
       </c>
       <c r="B120" s="1">
@@ -3944,15 +4052,16 @@
         <v>20</v>
       </c>
       <c r="F120" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G120" s="1">
-        <v>2000</v>
+        <f t="shared" si="8"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400602</v>
       </c>
       <c r="B121" s="1">
@@ -3966,15 +4075,16 @@
         <v>60</v>
       </c>
       <c r="F121" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G121" s="1">
-        <v>3000</v>
+        <f t="shared" si="8"/>
+        <v>4100</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400603</v>
       </c>
       <c r="B122" s="1">
@@ -3988,15 +4098,16 @@
         <v>180</v>
       </c>
       <c r="F122" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G122" s="1">
-        <v>4000</v>
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400604</v>
       </c>
       <c r="B123" s="1">
@@ -4010,15 +4121,16 @@
         <v>540</v>
       </c>
       <c r="F123" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G123" s="1">
-        <v>5000</v>
+        <f t="shared" si="8"/>
+        <v>5300</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>400605</v>
       </c>
       <c r="B124" s="1">
@@ -4032,15 +4144,16 @@
         <v>999999</v>
       </c>
       <c r="F124" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G124" s="1">
-        <v>6000</v>
+        <f t="shared" si="8"/>
+        <v>5900</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="1">
-        <f t="shared" ref="A125:A139" si="6">B125*100+D125</f>
+        <f t="shared" ref="A125:A139" si="10">B125*100+D125</f>
         <v>500101</v>
       </c>
       <c r="B125" s="1">
@@ -4056,15 +4169,15 @@
         <v>20</v>
       </c>
       <c r="F125" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G125" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500102</v>
       </c>
       <c r="B126" s="1">
@@ -4078,15 +4191,15 @@
         <v>60</v>
       </c>
       <c r="F126" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G126" s="1">
-        <v>3000</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500103</v>
       </c>
       <c r="B127" s="1">
@@ -4100,15 +4213,15 @@
         <v>180</v>
       </c>
       <c r="F127" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G127" s="1">
-        <v>4000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500104</v>
       </c>
       <c r="B128" s="1">
@@ -4122,15 +4235,15 @@
         <v>540</v>
       </c>
       <c r="F128" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G128" s="1">
-        <v>5000</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500105</v>
       </c>
       <c r="B129" s="1">
@@ -4144,15 +4257,15 @@
         <v>999999</v>
       </c>
       <c r="F129" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G129" s="1">
-        <v>6000</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500201</v>
       </c>
       <c r="B130" s="1">
@@ -4168,15 +4281,16 @@
         <v>20</v>
       </c>
       <c r="F130" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G130" s="1">
-        <v>2000</v>
+        <f>G125</f>
+        <v>4000</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500202</v>
       </c>
       <c r="B131" s="1">
@@ -4190,15 +4304,16 @@
         <v>60</v>
       </c>
       <c r="F131" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G131" s="1">
-        <v>3000</v>
+        <f t="shared" ref="G131:G154" si="11">G126</f>
+        <v>4600</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500203</v>
       </c>
       <c r="B132" s="1">
@@ -4212,15 +4327,16 @@
         <v>180</v>
       </c>
       <c r="F132" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G132" s="1">
-        <v>4000</v>
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500204</v>
       </c>
       <c r="B133" s="1">
@@ -4234,15 +4350,16 @@
         <v>540</v>
       </c>
       <c r="F133" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G133" s="1">
-        <v>5000</v>
+        <f t="shared" si="11"/>
+        <v>5800</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500205</v>
       </c>
       <c r="B134" s="1">
@@ -4256,15 +4373,16 @@
         <v>999999</v>
       </c>
       <c r="F134" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G134" s="1">
-        <v>6000</v>
+        <f t="shared" si="11"/>
+        <v>6400</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500301</v>
       </c>
       <c r="B135" s="1">
@@ -4280,15 +4398,16 @@
         <v>20</v>
       </c>
       <c r="F135" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G135" s="1">
-        <v>2000</v>
+        <f t="shared" si="11"/>
+        <v>4000</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500302</v>
       </c>
       <c r="B136" s="1">
@@ -4302,15 +4421,16 @@
         <v>60</v>
       </c>
       <c r="F136" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G136" s="1">
-        <v>3000</v>
+        <f t="shared" si="11"/>
+        <v>4600</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500303</v>
       </c>
       <c r="B137" s="1">
@@ -4324,15 +4444,16 @@
         <v>180</v>
       </c>
       <c r="F137" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G137" s="1">
-        <v>4000</v>
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500304</v>
       </c>
       <c r="B138" s="1">
@@ -4346,15 +4467,16 @@
         <v>540</v>
       </c>
       <c r="F138" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G138" s="1">
-        <v>5000</v>
+        <f t="shared" si="11"/>
+        <v>5800</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500305</v>
       </c>
       <c r="B139" s="1">
@@ -4368,15 +4490,16 @@
         <v>999999</v>
       </c>
       <c r="F139" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G139" s="1">
-        <v>6000</v>
+        <f t="shared" si="11"/>
+        <v>6400</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="1">
-        <f t="shared" ref="A140:A154" si="7">B140*100+D140</f>
+        <f t="shared" ref="A140:A159" si="12">B140*100+D140</f>
         <v>500401</v>
       </c>
       <c r="B140" s="1">
@@ -4392,15 +4515,16 @@
         <v>20</v>
       </c>
       <c r="F140" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G140" s="1">
-        <v>2000</v>
+        <f t="shared" si="11"/>
+        <v>4000</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500402</v>
       </c>
       <c r="B141" s="1">
@@ -4414,15 +4538,16 @@
         <v>60</v>
       </c>
       <c r="F141" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G141" s="1">
-        <v>3000</v>
+        <f t="shared" si="11"/>
+        <v>4600</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500403</v>
       </c>
       <c r="B142" s="1">
@@ -4436,15 +4561,16 @@
         <v>180</v>
       </c>
       <c r="F142" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G142" s="1">
-        <v>4000</v>
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500404</v>
       </c>
       <c r="B143" s="1">
@@ -4458,15 +4584,16 @@
         <v>540</v>
       </c>
       <c r="F143" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G143" s="1">
-        <v>5000</v>
+        <f t="shared" si="11"/>
+        <v>5800</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500405</v>
       </c>
       <c r="B144" s="1">
@@ -4480,15 +4607,16 @@
         <v>999999</v>
       </c>
       <c r="F144" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G144" s="1">
-        <v>6000</v>
+        <f t="shared" si="11"/>
+        <v>6400</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500501</v>
       </c>
       <c r="B145" s="1">
@@ -4504,15 +4632,16 @@
         <v>20</v>
       </c>
       <c r="F145" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G145" s="1">
-        <v>2000</v>
+        <f t="shared" si="11"/>
+        <v>4000</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500502</v>
       </c>
       <c r="B146" s="1">
@@ -4526,15 +4655,16 @@
         <v>60</v>
       </c>
       <c r="F146" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G146" s="1">
-        <v>3000</v>
+        <f t="shared" si="11"/>
+        <v>4600</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500503</v>
       </c>
       <c r="B147" s="1">
@@ -4548,15 +4678,16 @@
         <v>180</v>
       </c>
       <c r="F147" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G147" s="1">
-        <v>4000</v>
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500504</v>
       </c>
       <c r="B148" s="1">
@@ -4570,15 +4701,16 @@
         <v>540</v>
       </c>
       <c r="F148" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G148" s="1">
-        <v>5000</v>
+        <f t="shared" si="11"/>
+        <v>5800</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500505</v>
       </c>
       <c r="B149" s="1">
@@ -4592,15 +4724,16 @@
         <v>999999</v>
       </c>
       <c r="F149" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G149" s="1">
-        <v>6000</v>
+        <f t="shared" si="11"/>
+        <v>6400</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500601</v>
       </c>
       <c r="B150" s="1">
@@ -4616,15 +4749,16 @@
         <v>20</v>
       </c>
       <c r="F150" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G150" s="1">
-        <v>2000</v>
+        <f t="shared" si="11"/>
+        <v>4000</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500602</v>
       </c>
       <c r="B151" s="1">
@@ -4638,15 +4772,16 @@
         <v>60</v>
       </c>
       <c r="F151" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G151" s="1">
-        <v>3000</v>
+        <f t="shared" si="11"/>
+        <v>4600</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500603</v>
       </c>
       <c r="B152" s="1">
@@ -4660,15 +4795,16 @@
         <v>180</v>
       </c>
       <c r="F152" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G152" s="1">
-        <v>4000</v>
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500604</v>
       </c>
       <c r="B153" s="1">
@@ -4682,15 +4818,16 @@
         <v>540</v>
       </c>
       <c r="F153" s="1">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G153" s="1">
-        <v>5000</v>
+        <f t="shared" si="11"/>
+        <v>5800</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>500605</v>
       </c>
       <c r="B154" s="1">
@@ -4704,120 +4841,121 @@
         <v>999999</v>
       </c>
       <c r="F154" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G154" s="1">
-        <v>6000</v>
+        <f t="shared" si="11"/>
+        <v>6400</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="1">
-        <f>B155*100+D155</f>
+        <f t="shared" si="12"/>
         <v>900101</v>
       </c>
-      <c r="B155" s="6">
+      <c r="B155" s="1">
         <v>9001</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C155" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="1">
         <v>1</v>
       </c>
-      <c r="E155" s="6">
+      <c r="E155" s="1">
         <v>999999</v>
       </c>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="1">
-        <f>B156*100+D156</f>
+        <f t="shared" si="12"/>
         <v>900201</v>
       </c>
-      <c r="B156" s="6">
+      <c r="B156" s="1">
         <v>9002</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C156" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D156" s="1">
         <v>1</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E156" s="1">
         <v>999999</v>
       </c>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="1">
-        <f>B157*100+D157</f>
+        <f t="shared" si="12"/>
         <v>900301</v>
       </c>
-      <c r="B157" s="6">
+      <c r="B157" s="1">
         <v>9003</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D157" s="1">
         <v>1</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="1">
         <v>999999</v>
       </c>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="1">
-        <f>B158*100+D158</f>
+        <f t="shared" si="12"/>
         <v>900401</v>
       </c>
-      <c r="B158" s="6">
+      <c r="B158" s="1">
         <v>9004</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D158" s="1">
         <v>1</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E158" s="1">
         <v>999999</v>
       </c>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="1">
-        <f>B159*100+D159</f>
+        <f t="shared" si="12"/>
         <v>900501</v>
       </c>
-      <c r="B159" s="6">
+      <c r="B159" s="1">
         <v>9005</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C159" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D159" s="1">
         <v>1</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E159" s="1">
         <v>999999</v>
       </c>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
     </row>
     <row r="189" ht="14.25" spans="5:5">
-      <c r="E189" s="7"/>
+      <c r="E189" s="6"/>
     </row>
     <row r="205" ht="14.25" spans="5:5">
-      <c r="E205" s="7"/>
+      <c r="E205" s="6"/>
     </row>
     <row r="206" ht="14.25" spans="5:5">
-      <c r="E206" s="7"/>
+      <c r="E206" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4825,4 +4963,349 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="J15:Q35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="15" spans="10:14">
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="10:17">
+      <c r="J17">
+        <v>10</v>
+      </c>
+      <c r="K17">
+        <v>15</v>
+      </c>
+      <c r="L17">
+        <v>20</v>
+      </c>
+      <c r="M17">
+        <v>25</v>
+      </c>
+      <c r="N17">
+        <v>30</v>
+      </c>
+      <c r="P17">
+        <v>5</v>
+      </c>
+      <c r="Q17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="10:17">
+      <c r="J18">
+        <v>15</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>25</v>
+      </c>
+      <c r="M18">
+        <v>30</v>
+      </c>
+      <c r="N18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="10:17">
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>25</v>
+      </c>
+      <c r="L19">
+        <v>30</v>
+      </c>
+      <c r="M19">
+        <v>35</v>
+      </c>
+      <c r="N19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="10:17">
+      <c r="J20">
+        <v>25</v>
+      </c>
+      <c r="K20">
+        <v>30</v>
+      </c>
+      <c r="L20">
+        <v>35</v>
+      </c>
+      <c r="M20">
+        <v>40</v>
+      </c>
+      <c r="N20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="10:17">
+      <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21">
+        <v>35</v>
+      </c>
+      <c r="L21">
+        <v>40</v>
+      </c>
+      <c r="M21">
+        <v>45</v>
+      </c>
+      <c r="N21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="10:17">
+      <c r="J24">
+        <f t="shared" ref="J24:N24" si="0">J17+$P$13+$Q$13</f>
+        <v>10</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
+      </c>
+      <c r="Q24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="10:17">
+      <c r="J25">
+        <f t="shared" ref="J25:N25" si="1">J18+$P$13+$Q$13</f>
+        <v>15</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="10:17">
+      <c r="J26">
+        <f t="shared" ref="J26:N26" si="2">J19+$P$13+$Q$13</f>
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="10:17">
+      <c r="J27">
+        <f t="shared" ref="J27:N27" si="3">J20+$P$13+$Q$13</f>
+        <v>25</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="10:17">
+      <c r="J28">
+        <f t="shared" ref="J28:N28" si="4">J21+$P$13+$Q$13</f>
+        <v>30</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="10:17">
+      <c r="J31">
+        <v>20</v>
+      </c>
+      <c r="K31">
+        <f t="shared" ref="K31:N31" si="5">J31+$Q$20</f>
+        <v>20</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="10:17">
+      <c r="J32">
+        <f t="shared" ref="J32:N32" si="6">J31+$P$20</f>
+        <v>20</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="10:14">
+      <c r="J33">
+        <f t="shared" ref="J33:N33" si="7">J32+$P$20</f>
+        <v>20</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="10:14">
+      <c r="J34">
+        <f t="shared" ref="J34:N34" si="8">J33+$P$20</f>
+        <v>20</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="10:14">
+      <c r="J35">
+        <f t="shared" ref="J35:N35" si="9">J34+$P$20</f>
+        <v>20</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -1287,6 +1287,7 @@
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="18" max="18" width="12.625"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:7">
@@ -1381,7 +1382,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G5" s="1">
         <v>2000</v>
@@ -1403,7 +1404,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G6" s="1">
         <v>2600</v>
@@ -1425,7 +1426,7 @@
         <v>180</v>
       </c>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G7" s="1">
         <v>3200</v>
@@ -1447,7 +1448,7 @@
         <v>540</v>
       </c>
       <c r="F8" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G8" s="1">
         <v>3800</v>
@@ -1469,7 +1470,7 @@
         <v>999999</v>
       </c>
       <c r="F9" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G9" s="1">
         <v>4400</v>
@@ -1493,7 +1494,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1">
         <f>G5</f>
@@ -1516,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="F11" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G11" s="1">
         <f>G6</f>
@@ -1539,7 +1540,7 @@
         <v>180</v>
       </c>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G12" s="1">
         <f>G7</f>
@@ -1562,7 +1563,7 @@
         <v>540</v>
       </c>
       <c r="F13" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G13" s="1">
         <f>G8</f>
@@ -1585,7 +1586,7 @@
         <v>999999</v>
       </c>
       <c r="F14" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G14" s="1">
         <f>G9</f>
@@ -1610,7 +1611,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" ref="G15:G34" si="1">G10</f>
@@ -1633,7 +1634,7 @@
         <v>60</v>
       </c>
       <c r="F16" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="1"/>
@@ -1656,7 +1657,7 @@
         <v>180</v>
       </c>
       <c r="F17" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="1"/>
@@ -1679,7 +1680,7 @@
         <v>540</v>
       </c>
       <c r="F18" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="1"/>
@@ -1702,7 +1703,7 @@
         <v>999999</v>
       </c>
       <c r="F19" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="1"/>
@@ -1727,7 +1728,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="1"/>
@@ -1750,7 +1751,7 @@
         <v>60</v>
       </c>
       <c r="F21" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="1"/>
@@ -1773,7 +1774,7 @@
         <v>180</v>
       </c>
       <c r="F22" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="1"/>
@@ -1796,7 +1797,7 @@
         <v>540</v>
       </c>
       <c r="F23" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="1"/>
@@ -1819,7 +1820,7 @@
         <v>999999</v>
       </c>
       <c r="F24" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="1"/>
@@ -1844,7 +1845,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="1"/>
@@ -1867,7 +1868,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="1"/>
@@ -1890,7 +1891,7 @@
         <v>180</v>
       </c>
       <c r="F27" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="1"/>
@@ -1913,7 +1914,7 @@
         <v>540</v>
       </c>
       <c r="F28" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="1"/>
@@ -1936,7 +1937,7 @@
         <v>999999</v>
       </c>
       <c r="F29" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="1"/>
@@ -1961,7 +1962,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="1"/>
@@ -1984,7 +1985,7 @@
         <v>60</v>
       </c>
       <c r="F31" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="1"/>
@@ -2007,7 +2008,7 @@
         <v>180</v>
       </c>
       <c r="F32" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" si="1"/>
@@ -2030,7 +2031,7 @@
         <v>540</v>
       </c>
       <c r="F33" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" si="1"/>
@@ -2053,7 +2054,7 @@
         <v>999999</v>
       </c>
       <c r="F34" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="1"/>
@@ -2078,7 +2079,7 @@
         <v>20</v>
       </c>
       <c r="F35" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G35" s="1">
         <v>2500</v>
@@ -2100,7 +2101,7 @@
         <v>60</v>
       </c>
       <c r="F36" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G36" s="1">
         <v>3100</v>
@@ -2122,7 +2123,7 @@
         <v>180</v>
       </c>
       <c r="F37" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G37" s="1">
         <v>3700</v>
@@ -2144,7 +2145,7 @@
         <v>540</v>
       </c>
       <c r="F38" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G38" s="1">
         <v>4300</v>
@@ -2166,7 +2167,7 @@
         <v>999999</v>
       </c>
       <c r="F39" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G39" s="1">
         <v>4900</v>
@@ -2190,7 +2191,7 @@
         <v>20</v>
       </c>
       <c r="F40" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G40" s="1">
         <f>G35</f>
@@ -2213,7 +2214,7 @@
         <v>60</v>
       </c>
       <c r="F41" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" ref="G41:G64" si="3">G36</f>
@@ -2236,7 +2237,7 @@
         <v>180</v>
       </c>
       <c r="F42" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="3"/>
@@ -2259,7 +2260,7 @@
         <v>540</v>
       </c>
       <c r="F43" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="3"/>
@@ -2282,7 +2283,7 @@
         <v>999999</v>
       </c>
       <c r="F44" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="3"/>
@@ -2307,7 +2308,7 @@
         <v>20</v>
       </c>
       <c r="F45" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G45" s="1">
         <f t="shared" si="3"/>
@@ -2330,7 +2331,7 @@
         <v>60</v>
       </c>
       <c r="F46" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G46" s="1">
         <f t="shared" si="3"/>
@@ -2353,7 +2354,7 @@
         <v>180</v>
       </c>
       <c r="F47" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G47" s="1">
         <f t="shared" si="3"/>
@@ -2376,7 +2377,7 @@
         <v>540</v>
       </c>
       <c r="F48" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G48" s="1">
         <f t="shared" si="3"/>
@@ -2399,7 +2400,7 @@
         <v>999999</v>
       </c>
       <c r="F49" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G49" s="1">
         <f t="shared" si="3"/>
@@ -2424,7 +2425,7 @@
         <v>20</v>
       </c>
       <c r="F50" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="3"/>
@@ -2447,7 +2448,7 @@
         <v>60</v>
       </c>
       <c r="F51" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G51" s="1">
         <f t="shared" si="3"/>
@@ -2470,7 +2471,7 @@
         <v>180</v>
       </c>
       <c r="F52" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G52" s="1">
         <f t="shared" si="3"/>
@@ -2493,7 +2494,7 @@
         <v>540</v>
       </c>
       <c r="F53" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G53" s="1">
         <f t="shared" si="3"/>
@@ -2516,7 +2517,7 @@
         <v>999999</v>
       </c>
       <c r="F54" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="3"/>
@@ -2541,7 +2542,7 @@
         <v>20</v>
       </c>
       <c r="F55" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G55" s="1">
         <f t="shared" si="3"/>
@@ -2564,7 +2565,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G56" s="1">
         <f t="shared" si="3"/>
@@ -2587,7 +2588,7 @@
         <v>180</v>
       </c>
       <c r="F57" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G57" s="1">
         <f t="shared" si="3"/>
@@ -2610,7 +2611,7 @@
         <v>540</v>
       </c>
       <c r="F58" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G58" s="1">
         <f t="shared" si="3"/>
@@ -2633,7 +2634,7 @@
         <v>999999</v>
       </c>
       <c r="F59" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G59" s="1">
         <f t="shared" si="3"/>
@@ -2658,7 +2659,7 @@
         <v>20</v>
       </c>
       <c r="F60" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G60" s="1">
         <f t="shared" si="3"/>
@@ -2681,7 +2682,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G61" s="1">
         <f t="shared" si="3"/>
@@ -2704,7 +2705,7 @@
         <v>180</v>
       </c>
       <c r="F62" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G62" s="1">
         <f t="shared" si="3"/>
@@ -2727,7 +2728,7 @@
         <v>540</v>
       </c>
       <c r="F63" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G63" s="1">
         <f t="shared" si="3"/>
@@ -2750,7 +2751,7 @@
         <v>999999</v>
       </c>
       <c r="F64" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G64" s="1">
         <f t="shared" si="3"/>
@@ -2775,7 +2776,7 @@
         <v>20</v>
       </c>
       <c r="F65" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G65" s="1">
         <v>3000</v>
@@ -2797,7 +2798,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G66" s="1">
         <v>3600</v>
@@ -2819,7 +2820,7 @@
         <v>180</v>
       </c>
       <c r="F67" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G67" s="1">
         <v>4200</v>
@@ -2841,7 +2842,7 @@
         <v>540</v>
       </c>
       <c r="F68" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G68" s="1">
         <v>4800</v>
@@ -2863,7 +2864,7 @@
         <v>999999</v>
       </c>
       <c r="F69" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G69" s="1">
         <v>5400</v>
@@ -2887,7 +2888,7 @@
         <v>20</v>
       </c>
       <c r="F70" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G70" s="1">
         <f>G65</f>
@@ -2910,7 +2911,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G71" s="1">
         <f t="shared" ref="G71:G94" si="6">G66</f>
@@ -2933,7 +2934,7 @@
         <v>180</v>
       </c>
       <c r="F72" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="6"/>
@@ -2956,7 +2957,7 @@
         <v>540</v>
       </c>
       <c r="F73" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="6"/>
@@ -2979,7 +2980,7 @@
         <v>999999</v>
       </c>
       <c r="F74" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="6"/>
@@ -3004,7 +3005,7 @@
         <v>20</v>
       </c>
       <c r="F75" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="6"/>
@@ -3027,7 +3028,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="6"/>
@@ -3050,7 +3051,7 @@
         <v>180</v>
       </c>
       <c r="F77" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G77" s="1">
         <f t="shared" si="6"/>
@@ -3073,7 +3074,7 @@
         <v>540</v>
       </c>
       <c r="F78" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G78" s="1">
         <f t="shared" si="6"/>
@@ -3096,7 +3097,7 @@
         <v>999999</v>
       </c>
       <c r="F79" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G79" s="1">
         <f t="shared" si="6"/>
@@ -3121,7 +3122,7 @@
         <v>20</v>
       </c>
       <c r="F80" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G80" s="1">
         <f t="shared" si="6"/>
@@ -3144,7 +3145,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G81" s="1">
         <f t="shared" si="6"/>
@@ -3167,7 +3168,7 @@
         <v>180</v>
       </c>
       <c r="F82" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G82" s="1">
         <f t="shared" si="6"/>
@@ -3190,7 +3191,7 @@
         <v>540</v>
       </c>
       <c r="F83" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G83" s="1">
         <f t="shared" si="6"/>
@@ -3213,7 +3214,7 @@
         <v>999999</v>
       </c>
       <c r="F84" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G84" s="1">
         <f t="shared" si="6"/>
@@ -3238,7 +3239,7 @@
         <v>20</v>
       </c>
       <c r="F85" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G85" s="1">
         <f t="shared" si="6"/>
@@ -3261,7 +3262,7 @@
         <v>60</v>
       </c>
       <c r="F86" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G86" s="1">
         <f t="shared" si="6"/>
@@ -3284,7 +3285,7 @@
         <v>180</v>
       </c>
       <c r="F87" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G87" s="1">
         <f t="shared" si="6"/>
@@ -3307,7 +3308,7 @@
         <v>540</v>
       </c>
       <c r="F88" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G88" s="1">
         <f t="shared" si="6"/>
@@ -3330,7 +3331,7 @@
         <v>999999</v>
       </c>
       <c r="F89" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G89" s="1">
         <f t="shared" si="6"/>
@@ -3355,7 +3356,7 @@
         <v>20</v>
       </c>
       <c r="F90" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G90" s="1">
         <f t="shared" si="6"/>
@@ -3378,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G91" s="1">
         <f t="shared" si="6"/>
@@ -3401,7 +3402,7 @@
         <v>180</v>
       </c>
       <c r="F92" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G92" s="1">
         <f t="shared" si="6"/>
@@ -3424,7 +3425,7 @@
         <v>540</v>
       </c>
       <c r="F93" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G93" s="1">
         <f t="shared" si="6"/>
@@ -3447,7 +3448,7 @@
         <v>999999</v>
       </c>
       <c r="F94" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G94" s="1">
         <f t="shared" si="6"/>
@@ -3472,7 +3473,7 @@
         <v>20</v>
       </c>
       <c r="F95" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G95" s="1">
         <v>3500</v>
@@ -3494,7 +3495,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G96" s="1">
         <v>4100</v>
@@ -3516,7 +3517,7 @@
         <v>180</v>
       </c>
       <c r="F97" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G97" s="1">
         <v>4700</v>
@@ -3538,7 +3539,7 @@
         <v>540</v>
       </c>
       <c r="F98" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G98" s="1">
         <v>5300</v>
@@ -3560,7 +3561,7 @@
         <v>999999</v>
       </c>
       <c r="F99" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G99" s="1">
         <v>5900</v>
@@ -3584,7 +3585,7 @@
         <v>20</v>
       </c>
       <c r="F100" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G100" s="1">
         <f>G95</f>
@@ -3607,7 +3608,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G101" s="1">
         <f t="shared" ref="G101:G124" si="8">G96</f>
@@ -3630,7 +3631,7 @@
         <v>180</v>
       </c>
       <c r="F102" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G102" s="1">
         <f t="shared" si="8"/>
@@ -3653,7 +3654,7 @@
         <v>540</v>
       </c>
       <c r="F103" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
@@ -3676,7 +3677,7 @@
         <v>999999</v>
       </c>
       <c r="F104" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
@@ -3701,7 +3702,7 @@
         <v>20</v>
       </c>
       <c r="F105" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G105" s="1">
         <f t="shared" si="8"/>
@@ -3724,7 +3725,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G106" s="1">
         <f t="shared" si="8"/>
@@ -3747,7 +3748,7 @@
         <v>180</v>
       </c>
       <c r="F107" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G107" s="1">
         <f t="shared" si="8"/>
@@ -3770,7 +3771,7 @@
         <v>540</v>
       </c>
       <c r="F108" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G108" s="1">
         <f t="shared" si="8"/>
@@ -3793,7 +3794,7 @@
         <v>999999</v>
       </c>
       <c r="F109" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G109" s="1">
         <f t="shared" si="8"/>
@@ -3818,7 +3819,7 @@
         <v>20</v>
       </c>
       <c r="F110" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G110" s="1">
         <f t="shared" si="8"/>
@@ -3841,7 +3842,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G111" s="1">
         <f t="shared" si="8"/>
@@ -3864,7 +3865,7 @@
         <v>180</v>
       </c>
       <c r="F112" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G112" s="1">
         <f t="shared" si="8"/>
@@ -3887,7 +3888,7 @@
         <v>540</v>
       </c>
       <c r="F113" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G113" s="1">
         <f t="shared" si="8"/>
@@ -3910,7 +3911,7 @@
         <v>999999</v>
       </c>
       <c r="F114" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G114" s="1">
         <f t="shared" si="8"/>
@@ -3935,7 +3936,7 @@
         <v>20</v>
       </c>
       <c r="F115" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G115" s="1">
         <f t="shared" si="8"/>
@@ -3958,7 +3959,7 @@
         <v>60</v>
       </c>
       <c r="F116" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G116" s="1">
         <f t="shared" si="8"/>
@@ -3981,7 +3982,7 @@
         <v>180</v>
       </c>
       <c r="F117" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G117" s="1">
         <f t="shared" si="8"/>
@@ -4004,7 +4005,7 @@
         <v>540</v>
       </c>
       <c r="F118" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G118" s="1">
         <f t="shared" si="8"/>
@@ -4027,7 +4028,7 @@
         <v>999999</v>
       </c>
       <c r="F119" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G119" s="1">
         <f t="shared" si="8"/>
@@ -4052,7 +4053,7 @@
         <v>20</v>
       </c>
       <c r="F120" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G120" s="1">
         <f t="shared" si="8"/>
@@ -4075,7 +4076,7 @@
         <v>60</v>
       </c>
       <c r="F121" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G121" s="1">
         <f t="shared" si="8"/>
@@ -4098,7 +4099,7 @@
         <v>180</v>
       </c>
       <c r="F122" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G122" s="1">
         <f t="shared" si="8"/>
@@ -4121,7 +4122,7 @@
         <v>540</v>
       </c>
       <c r="F123" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G123" s="1">
         <f t="shared" si="8"/>
@@ -4144,7 +4145,7 @@
         <v>999999</v>
       </c>
       <c r="F124" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G124" s="1">
         <f t="shared" si="8"/>
@@ -4169,7 +4170,7 @@
         <v>20</v>
       </c>
       <c r="F125" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G125" s="1">
         <v>4000</v>
@@ -4191,7 +4192,7 @@
         <v>60</v>
       </c>
       <c r="F126" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G126" s="1">
         <v>4600</v>
@@ -4213,7 +4214,7 @@
         <v>180</v>
       </c>
       <c r="F127" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G127" s="1">
         <v>5200</v>
@@ -4235,7 +4236,7 @@
         <v>540</v>
       </c>
       <c r="F128" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G128" s="1">
         <v>5800</v>
@@ -4257,7 +4258,7 @@
         <v>999999</v>
       </c>
       <c r="F129" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G129" s="1">
         <v>6400</v>
@@ -4281,7 +4282,7 @@
         <v>20</v>
       </c>
       <c r="F130" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G130" s="1">
         <f>G125</f>
@@ -4304,7 +4305,7 @@
         <v>60</v>
       </c>
       <c r="F131" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G131" s="1">
         <f t="shared" ref="G131:G154" si="11">G126</f>
@@ -4327,7 +4328,7 @@
         <v>180</v>
       </c>
       <c r="F132" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G132" s="1">
         <f t="shared" si="11"/>
@@ -4350,7 +4351,7 @@
         <v>540</v>
       </c>
       <c r="F133" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G133" s="1">
         <f t="shared" si="11"/>
@@ -4373,7 +4374,7 @@
         <v>999999</v>
       </c>
       <c r="F134" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G134" s="1">
         <f t="shared" si="11"/>
@@ -4398,7 +4399,7 @@
         <v>20</v>
       </c>
       <c r="F135" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G135" s="1">
         <f t="shared" si="11"/>
@@ -4421,7 +4422,7 @@
         <v>60</v>
       </c>
       <c r="F136" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G136" s="1">
         <f t="shared" si="11"/>
@@ -4444,7 +4445,7 @@
         <v>180</v>
       </c>
       <c r="F137" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G137" s="1">
         <f t="shared" si="11"/>
@@ -4467,7 +4468,7 @@
         <v>540</v>
       </c>
       <c r="F138" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G138" s="1">
         <f t="shared" si="11"/>
@@ -4490,7 +4491,7 @@
         <v>999999</v>
       </c>
       <c r="F139" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G139" s="1">
         <f t="shared" si="11"/>
@@ -4515,7 +4516,7 @@
         <v>20</v>
       </c>
       <c r="F140" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G140" s="1">
         <f t="shared" si="11"/>
@@ -4538,7 +4539,7 @@
         <v>60</v>
       </c>
       <c r="F141" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G141" s="1">
         <f t="shared" si="11"/>
@@ -4561,7 +4562,7 @@
         <v>180</v>
       </c>
       <c r="F142" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G142" s="1">
         <f t="shared" si="11"/>
@@ -4584,7 +4585,7 @@
         <v>540</v>
       </c>
       <c r="F143" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G143" s="1">
         <f t="shared" si="11"/>
@@ -4607,7 +4608,7 @@
         <v>999999</v>
       </c>
       <c r="F144" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G144" s="1">
         <f t="shared" si="11"/>
@@ -4632,7 +4633,7 @@
         <v>20</v>
       </c>
       <c r="F145" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G145" s="1">
         <f t="shared" si="11"/>
@@ -4655,7 +4656,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G146" s="1">
         <f t="shared" si="11"/>
@@ -4678,7 +4679,7 @@
         <v>180</v>
       </c>
       <c r="F147" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G147" s="1">
         <f t="shared" si="11"/>
@@ -4701,7 +4702,7 @@
         <v>540</v>
       </c>
       <c r="F148" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G148" s="1">
         <f t="shared" si="11"/>
@@ -4724,7 +4725,7 @@
         <v>999999</v>
       </c>
       <c r="F149" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G149" s="1">
         <f t="shared" si="11"/>
@@ -4749,7 +4750,7 @@
         <v>20</v>
       </c>
       <c r="F150" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G150" s="1">
         <f t="shared" si="11"/>
@@ -4772,7 +4773,7 @@
         <v>60</v>
       </c>
       <c r="F151" s="1">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G151" s="1">
         <f t="shared" si="11"/>
@@ -4795,7 +4796,7 @@
         <v>180</v>
       </c>
       <c r="F152" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G152" s="1">
         <f t="shared" si="11"/>
@@ -4818,7 +4819,7 @@
         <v>540</v>
       </c>
       <c r="F153" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G153" s="1">
         <f t="shared" si="11"/>
@@ -4841,7 +4842,7 @@
         <v>999999</v>
       </c>
       <c r="F154" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G154" s="1">
         <f t="shared" si="11"/>

--- a/hall/resources/sample/VisitorStar.xlsx
+++ b/hall/resources/sample/VisitorStar.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorStar" sheetId="8" r:id="rId1"/>
@@ -1379,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1">
         <v>105</v>
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1">
         <v>110</v>
@@ -1445,7 +1445,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="F8" s="1">
         <v>115</v>
@@ -1491,7 +1491,8 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>20</v>
+        <f t="shared" ref="E10:E18" si="1">E5</f>
+        <v>5</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>
@@ -1514,7 +1515,8 @@
         <v>2</v>
       </c>
       <c r="E11" s="1">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="F11" s="1">
         <v>105</v>
@@ -1537,7 +1539,8 @@
         <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>180</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="F12" s="1">
         <v>110</v>
@@ -1560,7 +1563,8 @@
         <v>4</v>
       </c>
       <c r="E13" s="1">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="F13" s="1">
         <v>115</v>
@@ -1608,13 +1612,14 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" ref="G15:G34" si="1">G10</f>
+        <f t="shared" ref="G15:G34" si="2">G10</f>
         <v>2000</v>
       </c>
     </row>
@@ -1631,13 +1636,14 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="F16" s="1">
         <v>105</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2600</v>
       </c>
     </row>
@@ -1654,13 +1660,14 @@
         <v>3</v>
       </c>
       <c r="E17" s="1">
-        <v>180</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="F17" s="1">
         <v>110</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3200</v>
       </c>
     </row>
@@ -1677,13 +1684,14 @@
         <v>4</v>
       </c>
       <c r="E18" s="1">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="F18" s="1">
         <v>115</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3800</v>
       </c>
     </row>
@@ -1706,13 +1714,13 @@
         <v>120</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A49" si="2">B20*100+D20</f>
+        <f t="shared" ref="A20:A49" si="3">B20*100+D20</f>
         <v>100401</v>
       </c>
       <c r="B20" s="1">
@@ -1725,19 +1733,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>20</v>
+        <f t="shared" ref="E20:E23" si="4">E15</f>
+        <v>5</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100402</v>
       </c>
       <c r="B21" s="1">
@@ -1748,19 +1757,20 @@
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>60</v>
+        <f t="shared" si="4"/>
+        <v>10</v>
       </c>
       <c r="F21" s="1">
         <v>105</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2600</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100403</v>
       </c>
       <c r="B22" s="1">
@@ -1771,19 +1781,20 @@
         <v>3</v>
       </c>
       <c r="E22" s="1">
-        <v>180</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="F22" s="1">
         <v>110</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3200</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100404</v>
       </c>
       <c r="B23" s="1">
@@ -1794,19 +1805,20 @@
         <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>540</v>
+        <f t="shared" si="4"/>
+        <v>160</v>
       </c>
       <c r="F23" s="1">
         <v>115</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3800</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100405</v>
       </c>
       <c r="B24" s="1">
@@ -1823,13 +1835,13 @@
         <v>120</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100501</v>
       </c>
       <c r="B25" s="1">
@@ -1842,19 +1854,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>20</v>
+        <f t="shared" ref="E25:E28" si="5">E20</f>
+        <v>5</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100502</v>
       </c>
       <c r="B26" s="1">
@@ -1865,19 +1878,20 @@
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="F26" s="1">
         <v>105</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2600</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100503</v>
       </c>
       <c r="B27" s="1">
@@ -1888,19 +1902,20 @@
         <v>3</v>
       </c>
       <c r="E27" s="1">
-        <v>180</v>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="F27" s="1">
         <v>110</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3200</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100504</v>
       </c>
       <c r="B28" s="1">
@@ -1911,19 +1926,20 @@
         <v>4</v>
       </c>
       <c r="E28" s="1">
-        <v>540</v>
+        <f t="shared" si="5"/>
+        <v>160</v>
       </c>
       <c r="F28" s="1">
         <v>115</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3800</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100505</v>
       </c>
       <c r="B29" s="1">
@@ -1940,13 +1956,13 @@
         <v>120</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100601</v>
       </c>
       <c r="B30" s="1">
@@ -1959,19 +1975,20 @@
         <v>1</v>
       </c>
       <c r="E30" s="1">
-        <v>20</v>
+        <f t="shared" ref="E30:E33" si="6">E25</f>
+        <v>5</v>
       </c>
       <c r="F30" s="1">
         <v>100</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100602</v>
       </c>
       <c r="B31" s="1">
@@ -1982,19 +1999,20 @@
         <v>2</v>
       </c>
       <c r="E31" s="1">
-        <v>60</v>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="F31" s="1">
         <v>105</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2600</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100603</v>
       </c>
       <c r="B32" s="1">
@@ -2005,19 +2023,20 @@
         <v>3</v>
       </c>
       <c r="E32" s="1">
-        <v>180</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="F32" s="1">
         <v>110</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3200</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100604</v>
       </c>
       <c r="B33" s="1">
@@ -2028,19 +2047,20 @@
         <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>540</v>
+        <f t="shared" si="6"/>
+        <v>160</v>
       </c>
       <c r="F33" s="1">
         <v>115</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3800</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100605</v>
       </c>
       <c r="B34" s="1">
@@ -2057,13 +2077,13 @@
         <v>120</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4400</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200101</v>
       </c>
       <c r="B35" s="1">
@@ -2087,7 +2107,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200102</v>
       </c>
       <c r="B36" s="1">
@@ -2109,7 +2129,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200103</v>
       </c>
       <c r="B37" s="1">
@@ -2131,7 +2151,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200104</v>
       </c>
       <c r="B38" s="1">
@@ -2153,7 +2173,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200105</v>
       </c>
       <c r="B39" s="1">
@@ -2175,7 +2195,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200201</v>
       </c>
       <c r="B40" s="1">
@@ -2200,7 +2220,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200202</v>
       </c>
       <c r="B41" s="1">
@@ -2217,13 +2237,13 @@
         <v>105</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" ref="G41:G64" si="3">G36</f>
+        <f t="shared" ref="G41:G64" si="7">G36</f>
         <v>3100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200203</v>
       </c>
       <c r="B42" s="1">
@@ -2240,13 +2260,13 @@
         <v>110</v>
       </c>
       <c r="G42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3700</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200204</v>
       </c>
       <c r="B43" s="1">
@@ -2263,13 +2283,13 @@
         <v>115</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4300</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200205</v>
       </c>
       <c r="B44" s="1">
@@ -2286,13 +2306,13 @@
         <v>120</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4900</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200301</v>
       </c>
       <c r="B45" s="1">
@@ -2311,13 +2331,13 @@
         <v>100</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200302</v>
       </c>
       <c r="B46" s="1">
@@ -2334,13 +2354,13 @@
         <v>105</v>
       </c>
       <c r="G46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200303</v>
       </c>
       <c r="B47" s="1">
@@ -2357,13 +2377,13 @@
         <v>110</v>
       </c>
       <c r="G47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3700</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200304</v>
       </c>
       <c r="B48" s="1">
@@ -2380,13 +2400,13 @@
         <v>115</v>
       </c>
       <c r="G48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4300</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>200305</v>
       </c>
       <c r="B49" s="1">
@@ -2403,13 +2423,13 @@
         <v>120</v>
       </c>
       <c r="G49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4900</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1">
-        <f t="shared" ref="A50:A64" si="4">B50*100+D50</f>
+        <f t="shared" ref="A50:A64" si="8">B50*100+D50</f>
         <v>200401</v>
       </c>
       <c r="B50" s="1">
@@ -2428,13 +2448,13 @@
         <v>100</v>
       </c>
       <c r="G50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200402</v>
       </c>
       <c r="B51" s="1">
@@ -2451,13 +2471,13 @@
         <v>105</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3100</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200403</v>
       </c>
       <c r="B52" s="1">
@@ -2474,13 +2494,13 @@
         <v>110</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3700</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200404</v>
       </c>
       <c r="B53" s="1">
@@ -2497,13 +2517,13 @@
         <v>115</v>
       </c>
       <c r="G53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4300</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200405</v>
       </c>
       <c r="B54" s="1">
@@ -2520,13 +2540,13 @@
         <v>120</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4900</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200501</v>
       </c>
       <c r="B55" s="1">
@@ -2545,13 +2565,13 @@
         <v>100</v>
       </c>
       <c r="G55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200502</v>
       </c>
       <c r="B56" s="1">
@@ -2568,13 +2588,13 @@
         <v>105</v>
       </c>
       <c r="G56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3100</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200503</v>
       </c>
       <c r="B57" s="1">
@@ -2591,13 +2611,13 @@
         <v>110</v>
       </c>
       <c r="G57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3700</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200504</v>
       </c>
       <c r="B58" s="1">
@@ -2614,13 +2634,13 @@
         <v>115</v>
       </c>
       <c r="G58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4300</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200505</v>
       </c>
       <c r="B59" s="1">
@@ -2637,13 +2657,13 @@
         <v>120</v>
       </c>
       <c r="G59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4900</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200601</v>
       </c>
       <c r="B60" s="1">
@@ -2662,13 +2682,13 @@
         <v>100</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200602</v>
       </c>
       <c r="B61" s="1">
@@ -2685,13 +2705,13 @@
         <v>105</v>
       </c>
       <c r="G61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3100</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200603</v>
       </c>
       <c r="B62" s="1">
@@ -2708,13 +2728,13 @@
         <v>110</v>
       </c>
       <c r="G62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3700</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200604</v>
       </c>
       <c r="B63" s="1">
@@ -2731,13 +2751,13 @@
         <v>115</v>
       </c>
       <c r="G63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4300</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>200605</v>
       </c>
       <c r="B64" s="1">
@@ -2754,13 +2774,13 @@
         <v>120</v>
       </c>
       <c r="G64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4900</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
-        <f t="shared" ref="A65:A81" si="5">B65*100+D65</f>
+        <f t="shared" ref="A65:A81" si="9">B65*100+D65</f>
         <v>300101</v>
       </c>
       <c r="B65" s="1">
@@ -2784,7 +2804,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300102</v>
       </c>
       <c r="B66" s="1">
@@ -2806,7 +2826,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300103</v>
       </c>
       <c r="B67" s="1">
@@ -2828,7 +2848,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300104</v>
       </c>
       <c r="B68" s="1">
@@ -2850,7 +2870,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300105</v>
       </c>
       <c r="B69" s="1">
@@ -2872,7 +2892,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300201</v>
       </c>
       <c r="B70" s="1">
@@ -2897,7 +2917,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300202</v>
       </c>
       <c r="B71" s="1">
@@ -2914,13 +2934,13 @@
         <v>105</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" ref="G71:G94" si="6">G66</f>
+        <f t="shared" ref="G71:G94" si="10">G66</f>
         <v>3600</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300203</v>
       </c>
       <c r="B72" s="1">
@@ -2937,13 +2957,13 @@
         <v>110</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4200</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300204</v>
       </c>
       <c r="B73" s="1">
@@ -2960,13 +2980,13 @@
         <v>115</v>
       </c>
       <c r="G73" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4800</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300205</v>
       </c>
       <c r="B74" s="1">
@@ -2983,13 +3003,13 @@
         <v>120</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5400</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300301</v>
       </c>
       <c r="B75" s="1">
@@ -3008,13 +3028,13 @@
         <v>100</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3000</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300302</v>
       </c>
       <c r="B76" s="1">
@@ -3031,13 +3051,13 @@
         <v>105</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3600</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300303</v>
       </c>
       <c r="B77" s="1">
@@ -3054,13 +3074,13 @@
         <v>110</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4200</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300304</v>
       </c>
       <c r="B78" s="1">
@@ -3077,13 +3097,13 @@
         <v>115</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4800</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>300305</v>
       </c>
       <c r="B79" s="1">
@@ -3100,13 +3120,13 @@
         <v>120</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5400</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1">
-        <f t="shared" ref="A80:A109" si="7">B80*100+D80</f>
+        <f t="shared" ref="A80:A109" si="11">B80*100+D80</f>
         <v>300401</v>
       </c>
       <c r="B80" s="1">
@@ -3125,13 +3145,13 @@
         <v>100</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3000</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300402</v>
       </c>
       <c r="B81" s="1">
@@ -3148,13 +3168,13 @@
         <v>105</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3600</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300403</v>
       </c>
       <c r="B82" s="1">
@@ -3171,13 +3191,13 @@
         <v>110</v>
       </c>
       <c r="G82" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4200</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300404</v>
       </c>
       <c r="B83" s="1">
@@ -3194,13 +3214,13 @@
         <v>115</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4800</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300405</v>
       </c>
       <c r="B84" s="1">
@@ -3217,13 +3237,13 @@
         <v>120</v>
       </c>
       <c r="G84" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5400</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300501</v>
       </c>
       <c r="B85" s="1">
@@ -3242,13 +3262,13 @@
         <v>100</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3000</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300502</v>
       </c>
       <c r="B86" s="1">
@@ -3265,13 +3285,13 @@
         <v>105</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3600</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300503</v>
       </c>
       <c r="B87" s="1">
@@ -3288,13 +3308,13 @@
         <v>110</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4200</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300504</v>
       </c>
       <c r="B88" s="1">
@@ -3311,13 +3331,13 @@
         <v>115</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4800</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300505</v>
       </c>
       <c r="B89" s="1">
@@ -3334,13 +3354,13 @@
         <v>120</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5400</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300601</v>
       </c>
       <c r="B90" s="1">
@@ -3359,13 +3379,13 @@
         <v>100</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3000</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300602</v>
       </c>
       <c r="B91" s="1">
@@ -3382,13 +3402,13 @@
         <v>105</v>
       </c>
       <c r="G91" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3600</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300603</v>
       </c>
       <c r="B92" s="1">
@@ -3405,13 +3425,13 @@
         <v>110</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4200</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300604</v>
       </c>
       <c r="B93" s="1">
@@ -3428,13 +3448,13 @@
         <v>115</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4800</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300605</v>
       </c>
       <c r="B94" s="1">
@@ -3451,13 +3471,13 @@
         <v>120</v>
       </c>
       <c r="G94" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5400</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400101</v>
       </c>
       <c r="B95" s="1">
@@ -3481,7 +3501,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400102</v>
       </c>
       <c r="B96" s="1">
@@ -3503,7 +3523,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400103</v>
       </c>
       <c r="B97" s="1">
@@ -3525,7 +3545,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400104</v>
       </c>
       <c r="B98" s="1">
@@ -3547,7 +3567,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400105</v>
       </c>
       <c r="B99" s="1">
@@ -3569,7 +3589,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400201</v>
       </c>
       <c r="B100" s="1">
@@ -3594,7 +3614,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400202</v>
       </c>
       <c r="B101" s="1">
@@ -3611,13 +3631,13 @@
         <v>105</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" ref="G101:G124" si="8">G96</f>
+        <f t="shared" ref="G101:G124" si="12">G96</f>
         <v>4100</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400203</v>
       </c>
       <c r="B102" s="1">
@@ -3634,13 +3654,13 @@
         <v>110</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4700</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400204</v>
       </c>
       <c r="B103" s="1">
@@ -3657,13 +3677,13 @@
         <v>115</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5300</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400205</v>
       </c>
       <c r="B104" s="1">
@@ -3680,13 +3700,13 @@
         <v>120</v>
       </c>
       <c r="G104" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5900</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400301</v>
       </c>
       <c r="B105" s="1">
@@ -3705,13 +3725,13 @@
         <v>100</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400302</v>
       </c>
       <c r="B106" s="1">
@@ -3728,13 +3748,13 @@
         <v>105</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4100</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400303</v>
       </c>
       <c r="B107" s="1">
@@ -3751,13 +3771,13 @@
         <v>110</v>
       </c>
       <c r="G107" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4700</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400304</v>
       </c>
       <c r="B108" s="1">
@@ -3774,13 +3794,13 @@
         <v>115</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5300</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>400305</v>
       </c>
       <c r="B109" s="1">
@@ -3797,13 +3817,13 @@
         <v>120</v>
       </c>
       <c r="G109" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5900</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="1">
-        <f t="shared" ref="A110:A124" si="9">B110*100+D110</f>
+        <f t="shared" ref="A110:A124" si="13">B110*100+D110</f>
         <v>400401</v>
       </c>
       <c r="B110" s="1">
@@ -3822,13 +3842,13 @@
         <v>100</v>
       </c>
       <c r="G110" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400402</v>
       </c>
       <c r="B111" s="1">
@@ -3845,13 +3865,13 @@
         <v>105</v>
       </c>
       <c r="G111" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4100</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400403</v>
       </c>
       <c r="B112" s="1">
@@ -3868,13 +3888,13 @@
         <v>110</v>
       </c>
       <c r="G112" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4700</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400404</v>
       </c>
       <c r="B113" s="1">
@@ -3891,13 +3911,13 @@
         <v>115</v>
       </c>
       <c r="G113" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5300</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400405</v>
       </c>
       <c r="B114" s="1">
@@ -3914,13 +3934,13 @@
         <v>120</v>
       </c>
       <c r="G114" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5900</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400501</v>
       </c>
       <c r="B115" s="1">
@@ -3939,13 +3959,13 @@
         <v>100</v>
       </c>
       <c r="G115" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400502</v>
       </c>
       <c r="B116" s="1">
@@ -3962,13 +3982,13 @@
         <v>105</v>
       </c>
       <c r="G116" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4100</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400503</v>
       </c>
       <c r="B117" s="1">
@@ -3985,13 +4005,13 @@
         <v>110</v>
       </c>
       <c r="G117" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4700</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400504</v>
       </c>
       <c r="B118" s="1">
@@ -4008,13 +4028,13 @@
         <v>115</v>
       </c>
       <c r="G118" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5300</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400505</v>
       </c>
       <c r="B119" s="1">
@@ -4031,13 +4051,13 @@
         <v>120</v>
       </c>
       <c r="G119" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5900</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400601</v>
       </c>
       <c r="B120" s="1">
@@ -4056,13 +4076,13 @@
         <v>100</v>
       </c>
       <c r="G120" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400602</v>
       </c>
       <c r="B121" s="1">
@@ -4079,13 +4099,13 @@
         <v>105</v>
       </c>
       <c r="G121" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4100</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400603</v>
       </c>
       <c r="B122" s="1">
@@ -4102,13 +4122,13 @@
         <v>110</v>
       </c>
       <c r="G122" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4700</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400604</v>
       </c>
       <c r="B123" s="1">
@@ -4125,13 +4145,13 @@
         <v>115</v>
       </c>
       <c r="G123" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5300</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>400605</v>
       </c>
       <c r="B124" s="1">
@@ -4148,13 +4168,13 @@
         <v>120</v>
       </c>
       <c r="G124" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5900</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="1">
-        <f t="shared" ref="A125:A139" si="10">B125*100+D125</f>
+        <f t="shared" ref="A125:A139" si="14">B125*100+D125</f>
         <v>500101</v>
       </c>
       <c r="B125" s="1">
@@ -4178,7 +4198,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500102</v>
       </c>
       <c r="B126" s="1">
@@ -4200,7 +4220,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500103</v>
       </c>
       <c r="B127" s="1">
@@ -4222,7 +4242,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500104</v>
       </c>
       <c r="B128" s="1">
@@ -4244,7 +4264,7 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500105</v>
       </c>
       <c r="B129" s="1">
@@ -4266,7 +4286,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500201</v>
       </c>
       <c r="B130" s="1">
@@ -4291,7 +4311,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500202</v>
       </c>
       <c r="B131" s="1">
@@ -4308,13 +4328,13 @@
         <v>105</v>
       </c>
       <c r="G131" s="1">
-        <f t="shared" ref="G131:G154" si="11">G126</f>
+        <f t="shared" ref="G131:G154" si="15">G126</f>
         <v>4600</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500203</v>
       </c>
       <c r="B132" s="1">
@@ -4331,13 +4351,13 @@
         <v>110</v>
       </c>
       <c r="G132" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5200</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500204</v>
       </c>
       <c r="B133" s="1">
@@ -4354,13 +4374,13 @@
         <v>115</v>
       </c>
       <c r="G133" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5800</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500205</v>
       </c>
       <c r="B134" s="1">
@@ -4377,13 +4397,13 @@
         <v>120</v>
       </c>
       <c r="G134" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6400</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500301</v>
       </c>
       <c r="B135" s="1">
@@ -4402,13 +4422,13 @@
         <v>100</v>
       </c>
       <c r="G135" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4000</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500302</v>
       </c>
       <c r="B136" s="1">
@@ -4425,13 +4445,13 @@
         <v>105</v>
       </c>
       <c r="G136" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4600</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500303</v>
       </c>
       <c r="B137" s="1">
@@ -4448,13 +4468,13 @@
         <v>110</v>
       </c>
       <c r="G137" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5200</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500304</v>
       </c>
       <c r="B138" s="1">
@@ -4471,13 +4491,13 @@
         <v>115</v>
       </c>
       <c r="G138" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5800</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>500305</v>
       </c>
       <c r="B139" s="1">
@@ -4494,13 +4514,13 @@
         <v>120</v>
       </c>
       <c r="G139" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6400</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="1">
-        <f t="shared" ref="A140:A159" si="12">B140*100+D140</f>
+        <f t="shared" ref="A140:A159" si="16">B140*100+D140</f>
         <v>500401</v>
       </c>
       <c r="B140" s="1">
@@ -4519,13 +4539,13 @@
         <v>100</v>
       </c>
       <c r="G140" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4000</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500402</v>
       </c>
       <c r="B141" s="1">
@@ -4542,13 +4562,13 @@
         <v>105</v>
       </c>
       <c r="G141" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4600</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500403</v>
       </c>
       <c r="B142" s="1">
@@ -4565,13 +4585,13 @@
         <v>110</v>
       </c>
       <c r="G142" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5200</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500404</v>
       </c>
       <c r="B143" s="1">
@@ -4588,13 +4608,13 @@
         <v>115</v>
       </c>
       <c r="G143" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5800</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500405</v>
       </c>
       <c r="B144" s="1">
@@ -4611,13 +4631,13 @@
         <v>120</v>
       </c>
       <c r="G144" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6400</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500501</v>
       </c>
       <c r="B145" s="1">
@@ -4636,13 +4656,13 @@
         <v>100</v>
       </c>
       <c r="G145" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4000</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500502</v>
       </c>
       <c r="B146" s="1">
@@ -4659,13 +4679,13 @@
         <v>105</v>
       </c>
       <c r="G146" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4600</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500503</v>
       </c>
       <c r="B147" s="1">
@@ -4682,13 +4702,13 @@
         <v>110</v>
       </c>
       <c r="G147" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5200</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500504</v>
       </c>
       <c r="B148" s="1">
@@ -4705,13 +4725,13 @@
         <v>115</v>
       </c>
       <c r="G148" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5800</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500505</v>
       </c>
       <c r="B149" s="1">
@@ -4728,13 +4748,13 @@
         <v>120</v>
       </c>
       <c r="G149" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6400</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500601</v>
       </c>
       <c r="B150" s="1">
@@ -4753,13 +4773,13 @@
         <v>100</v>
       </c>
       <c r="G150" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4000</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500602</v>
       </c>
       <c r="B151" s="1">
@@ -4776,13 +4796,13 @@
         <v>105</v>
       </c>
       <c r="G151" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4600</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500603</v>
       </c>
       <c r="B152" s="1">
@@ -4799,13 +4819,13 @@
         <v>110</v>
       </c>
       <c r="G152" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5200</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500604</v>
       </c>
       <c r="B153" s="1">
@@ -4822,13 +4842,13 @@
         <v>115</v>
       </c>
       <c r="G153" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5800</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>500605</v>
       </c>
       <c r="B154" s="1">
@@ -4845,13 +4865,13 @@
         <v>120</v>
       </c>
       <c r="G154" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6400</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>900101</v>
       </c>
       <c r="B155" s="1">
@@ -4871,7 +4891,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>900201</v>
       </c>
       <c r="B156" s="1">
@@ -4891,7 +4911,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>900301</v>
       </c>
       <c r="B157" s="1">
@@ -4911,7 +4931,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>900401</v>
       </c>
       <c r="B158" s="1">
@@ -4931,7 +4951,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>900501</v>
       </c>
       <c r="B159" s="1">
